--- a/data/nzd0067/nzd0067.xlsx
+++ b/data/nzd0067/nzd0067.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH213"/>
+  <dimension ref="A1:AH214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23364,6 +23364,114 @@
       <c r="AH213" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>411.96</v>
+      </c>
+      <c r="C214" t="n">
+        <v>423.55</v>
+      </c>
+      <c r="D214" t="n">
+        <v>431.66</v>
+      </c>
+      <c r="E214" t="n">
+        <v>436.67</v>
+      </c>
+      <c r="F214" t="n">
+        <v>436.15</v>
+      </c>
+      <c r="G214" t="n">
+        <v>434.92</v>
+      </c>
+      <c r="H214" t="n">
+        <v>433.14</v>
+      </c>
+      <c r="I214" t="n">
+        <v>434.98</v>
+      </c>
+      <c r="J214" t="n">
+        <v>432.42</v>
+      </c>
+      <c r="K214" t="n">
+        <v>430.19</v>
+      </c>
+      <c r="L214" t="n">
+        <v>429</v>
+      </c>
+      <c r="M214" t="n">
+        <v>428.32</v>
+      </c>
+      <c r="N214" t="n">
+        <v>427.66</v>
+      </c>
+      <c r="O214" t="n">
+        <v>429.02</v>
+      </c>
+      <c r="P214" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="R214" t="n">
+        <v>387.69</v>
+      </c>
+      <c r="S214" t="n">
+        <v>386.35</v>
+      </c>
+      <c r="T214" t="n">
+        <v>398.92</v>
+      </c>
+      <c r="U214" t="n">
+        <v>397.23</v>
+      </c>
+      <c r="V214" t="n">
+        <v>393.38</v>
+      </c>
+      <c r="W214" t="n">
+        <v>387.76</v>
+      </c>
+      <c r="X214" t="n">
+        <v>386.06</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>378.01</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>377.51</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>373.47</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>344.37</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>326.98</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23378,7 +23486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B219"/>
+  <dimension ref="A1:B220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25571,6 +25679,16 @@
       </c>
       <c r="B219" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -25739,28 +25857,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1786885049544713</v>
+        <v>0.1740652560191204</v>
       </c>
       <c r="J2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01522138427996067</v>
+        <v>0.01459584677419246</v>
       </c>
       <c r="M2" t="n">
-        <v>8.998758997929851</v>
+        <v>8.98055213591128</v>
       </c>
       <c r="N2" t="n">
-        <v>128.6728992559085</v>
+        <v>128.1836166542582</v>
       </c>
       <c r="O2" t="n">
-        <v>11.34340774440858</v>
+        <v>11.3218203772299</v>
       </c>
       <c r="P2" t="n">
-        <v>412.4187751605093</v>
+        <v>412.4605323280388</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25817,28 +25935,28 @@
         <v>0.0361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.163596499360672</v>
+        <v>0.1611025186161366</v>
       </c>
       <c r="J3" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01379295702187677</v>
+        <v>0.01352021100017819</v>
       </c>
       <c r="M3" t="n">
-        <v>8.260680690739878</v>
+        <v>8.235223649331399</v>
       </c>
       <c r="N3" t="n">
-        <v>118.6202737305237</v>
+        <v>118.0857752543805</v>
       </c>
       <c r="O3" t="n">
-        <v>10.89129348289374</v>
+        <v>10.86672790008016</v>
       </c>
       <c r="P3" t="n">
-        <v>422.022333519407</v>
+        <v>422.0450522343145</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25895,28 +26013,28 @@
         <v>0.0434</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2694118295644226</v>
+        <v>0.268082584850574</v>
       </c>
       <c r="J4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K4" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02588286935969975</v>
+        <v>0.02590448718482952</v>
       </c>
       <c r="M4" t="n">
-        <v>9.883259836835228</v>
+        <v>9.842721132366252</v>
       </c>
       <c r="N4" t="n">
-        <v>166.8847669530027</v>
+        <v>166.0846380882162</v>
       </c>
       <c r="O4" t="n">
-        <v>12.91838871349685</v>
+        <v>12.88738290298756</v>
       </c>
       <c r="P4" t="n">
-        <v>426.0510596388708</v>
+        <v>426.063361882113</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25973,28 +26091,28 @@
         <v>0.0469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3236708937634532</v>
+        <v>0.3240768640869354</v>
       </c>
       <c r="J5" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03785796721619183</v>
+        <v>0.03834472011054535</v>
       </c>
       <c r="M5" t="n">
-        <v>10.02841226275232</v>
+        <v>9.982695335264021</v>
       </c>
       <c r="N5" t="n">
-        <v>165.9582939611441</v>
+        <v>165.1727153176875</v>
       </c>
       <c r="O5" t="n">
-        <v>12.88248011685421</v>
+        <v>12.85195375488441</v>
       </c>
       <c r="P5" t="n">
-        <v>427.746235228997</v>
+        <v>427.7425758999436</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26051,28 +26169,28 @@
         <v>0.045</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4636067573525778</v>
+        <v>0.4634026379828091</v>
       </c>
       <c r="J6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07250803555363339</v>
+        <v>0.07317634045453425</v>
       </c>
       <c r="M6" t="n">
-        <v>9.971797036223913</v>
+        <v>9.924878012226019</v>
       </c>
       <c r="N6" t="n">
-        <v>169.1881912744018</v>
+        <v>168.3750245389101</v>
       </c>
       <c r="O6" t="n">
-        <v>13.0072361120417</v>
+        <v>12.97594021791524</v>
       </c>
       <c r="P6" t="n">
-        <v>424.2376535256892</v>
+        <v>424.2395255989335</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26129,28 +26247,28 @@
         <v>0.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5891060928625163</v>
+        <v>0.5892742843939653</v>
       </c>
       <c r="J7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1312842443278164</v>
+        <v>0.132581707815413</v>
       </c>
       <c r="M7" t="n">
-        <v>9.66460047210759</v>
+        <v>9.620021325393601</v>
       </c>
       <c r="N7" t="n">
-        <v>144.365287736467</v>
+        <v>143.6876818298167</v>
       </c>
       <c r="O7" t="n">
-        <v>12.01521068215065</v>
+        <v>11.98697967921097</v>
       </c>
       <c r="P7" t="n">
-        <v>419.3150042040838</v>
+        <v>419.3135047462937</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26207,28 +26325,28 @@
         <v>0.0427</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6687233748558764</v>
+        <v>0.6679098109444517</v>
       </c>
       <c r="J8" t="n">
+        <v>213</v>
+      </c>
+      <c r="K8" t="n">
         <v>212</v>
       </c>
-      <c r="K8" t="n">
-        <v>211</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1714643060972582</v>
+        <v>0.1726433892376631</v>
       </c>
       <c r="M8" t="n">
-        <v>9.336285571628718</v>
+        <v>9.296066250457304</v>
       </c>
       <c r="N8" t="n">
-        <v>136.3861830940319</v>
+        <v>135.7467440798641</v>
       </c>
       <c r="O8" t="n">
-        <v>11.67844951584036</v>
+        <v>11.65104047198636</v>
       </c>
       <c r="P8" t="n">
-        <v>416.5512307782648</v>
+        <v>416.5584737312122</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26285,28 +26403,28 @@
         <v>0.0432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7212157695776371</v>
+        <v>0.723009822488593</v>
       </c>
       <c r="J9" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K9" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1896905235458819</v>
+        <v>0.1920988629561414</v>
       </c>
       <c r="M9" t="n">
-        <v>9.260781887322803</v>
+        <v>9.226446096695975</v>
       </c>
       <c r="N9" t="n">
-        <v>139.6839068093172</v>
+        <v>139.046932562077</v>
       </c>
       <c r="O9" t="n">
-        <v>11.81879464282704</v>
+        <v>11.79181633854925</v>
       </c>
       <c r="P9" t="n">
-        <v>414.0831435853148</v>
+        <v>414.0671492805477</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26363,28 +26481,28 @@
         <v>0.0369</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8598583667953532</v>
+        <v>0.859895691278071</v>
       </c>
       <c r="J10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2543143022850943</v>
+        <v>0.2563765932780021</v>
       </c>
       <c r="M10" t="n">
-        <v>9.276793575697917</v>
+        <v>9.233417251394238</v>
       </c>
       <c r="N10" t="n">
-        <v>136.2854629173187</v>
+        <v>135.6456332085584</v>
       </c>
       <c r="O10" t="n">
-        <v>11.67413649557511</v>
+        <v>11.64670052884328</v>
       </c>
       <c r="P10" t="n">
-        <v>409.875550310505</v>
+        <v>409.8752175560203</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26441,28 +26559,28 @@
         <v>0.0378</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8585036997896611</v>
+        <v>0.8576764952660551</v>
       </c>
       <c r="J11" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K11" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2299155450515555</v>
+        <v>0.2314782705408226</v>
       </c>
       <c r="M11" t="n">
-        <v>9.799383301061868</v>
+        <v>9.757128523028834</v>
       </c>
       <c r="N11" t="n">
-        <v>155.1904618112327</v>
+        <v>154.4658688851912</v>
       </c>
       <c r="O11" t="n">
-        <v>12.45754638005545</v>
+        <v>12.42842986403315</v>
       </c>
       <c r="P11" t="n">
-        <v>408.6488343902851</v>
+        <v>408.6562090675727</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26519,28 +26637,28 @@
         <v>0.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7374438203392184</v>
+        <v>0.7380878234897567</v>
       </c>
       <c r="J12" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K12" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1771590895150269</v>
+        <v>0.1789990393358929</v>
       </c>
       <c r="M12" t="n">
-        <v>9.952547181871344</v>
+        <v>9.90888556090831</v>
       </c>
       <c r="N12" t="n">
-        <v>155.6086480259752</v>
+        <v>154.8735248394379</v>
       </c>
       <c r="O12" t="n">
-        <v>12.47431954160127</v>
+        <v>12.44481919673556</v>
       </c>
       <c r="P12" t="n">
-        <v>408.9872855524737</v>
+        <v>408.9814281819231</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26597,28 +26715,28 @@
         <v>0.0375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6802650403607504</v>
+        <v>0.6844571771487208</v>
       </c>
       <c r="J13" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K13" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1500093118575567</v>
+        <v>0.1528905377097909</v>
       </c>
       <c r="M13" t="n">
-        <v>10.211508697213</v>
+        <v>10.18216336529799</v>
       </c>
       <c r="N13" t="n">
-        <v>164.8401179641288</v>
+        <v>164.168972864887</v>
       </c>
       <c r="O13" t="n">
-        <v>12.83900767053781</v>
+        <v>12.81284405840042</v>
       </c>
       <c r="P13" t="n">
-        <v>405.7980348554193</v>
+        <v>405.7606612010512</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26675,28 +26793,28 @@
         <v>0.0353</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6844761047425617</v>
+        <v>0.6892540083443958</v>
       </c>
       <c r="J14" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K14" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1561906360108255</v>
+        <v>0.1593569790865774</v>
       </c>
       <c r="M14" t="n">
-        <v>9.996483528512107</v>
+        <v>9.973942601879859</v>
       </c>
       <c r="N14" t="n">
-        <v>159.1170037633259</v>
+        <v>158.5034490220121</v>
       </c>
       <c r="O14" t="n">
-        <v>12.61415886071386</v>
+        <v>12.58981528943186</v>
       </c>
       <c r="P14" t="n">
-        <v>404.3690465722598</v>
+        <v>404.3264507012636</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26753,28 +26871,28 @@
         <v>0.0359</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6016604434669578</v>
+        <v>0.6097958051334057</v>
       </c>
       <c r="J15" t="n">
+        <v>213</v>
+      </c>
+      <c r="K15" t="n">
         <v>212</v>
       </c>
-      <c r="K15" t="n">
-        <v>211</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1265659202684206</v>
+        <v>0.1305087131157694</v>
       </c>
       <c r="M15" t="n">
-        <v>9.654978026226159</v>
+        <v>9.645184888787405</v>
       </c>
       <c r="N15" t="n">
-        <v>155.4123747043202</v>
+        <v>155.0607195617565</v>
       </c>
       <c r="O15" t="n">
-        <v>12.46644996397612</v>
+        <v>12.4523379154983</v>
       </c>
       <c r="P15" t="n">
-        <v>404.2148282647405</v>
+        <v>404.1415483201898</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26831,28 +26949,28 @@
         <v>0.0309</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3508445324113652</v>
+        <v>0.3621510473795633</v>
       </c>
       <c r="J16" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K16" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04787954210865175</v>
+        <v>0.05114657594754979</v>
       </c>
       <c r="M16" t="n">
-        <v>9.887688503563744</v>
+        <v>9.888856556826903</v>
       </c>
       <c r="N16" t="n">
-        <v>150.7977097632303</v>
+        <v>150.8100180068756</v>
       </c>
       <c r="O16" t="n">
-        <v>12.27997189586484</v>
+        <v>12.28047303677165</v>
       </c>
       <c r="P16" t="n">
-        <v>403.4361071533766</v>
+        <v>403.3332715573886</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26909,28 +27027,28 @@
         <v>0.0256</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0903326166221512</v>
+        <v>-0.08185795075722485</v>
       </c>
       <c r="J17" t="n">
+        <v>213</v>
+      </c>
+      <c r="K17" t="n">
         <v>212</v>
       </c>
-      <c r="K17" t="n">
-        <v>211</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.003180447884502668</v>
+        <v>0.002634678557091652</v>
       </c>
       <c r="M17" t="n">
-        <v>10.37855899338549</v>
+        <v>10.36968432246348</v>
       </c>
       <c r="N17" t="n">
-        <v>161.2220387017705</v>
+        <v>160.8801435825594</v>
       </c>
       <c r="O17" t="n">
-        <v>12.69732407642533</v>
+        <v>12.68385365662027</v>
       </c>
       <c r="P17" t="n">
-        <v>401.4472790726496</v>
+        <v>401.3719641922074</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26987,28 +27105,28 @@
         <v>0.0209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.236909908210417</v>
+        <v>0.2336546568369746</v>
       </c>
       <c r="J18" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K18" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01297372573646283</v>
+        <v>0.01275601155563155</v>
       </c>
       <c r="M18" t="n">
-        <v>13.42311503844613</v>
+        <v>13.38088982477726</v>
       </c>
       <c r="N18" t="n">
-        <v>268.4362183978762</v>
+        <v>267.2379112884701</v>
       </c>
       <c r="O18" t="n">
-        <v>16.38402326652023</v>
+        <v>16.34741298458169</v>
       </c>
       <c r="P18" t="n">
-        <v>385.1500946061626</v>
+        <v>385.1791157583496</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27065,28 +27183,28 @@
         <v>0.0255</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2123397912362648</v>
+        <v>0.2054837321641909</v>
       </c>
       <c r="J19" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K19" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01156173654402282</v>
+        <v>0.01093873021554004</v>
       </c>
       <c r="M19" t="n">
-        <v>12.19301951170562</v>
+        <v>12.17443367609748</v>
       </c>
       <c r="N19" t="n">
-        <v>242.3259446848166</v>
+        <v>241.4630974007473</v>
       </c>
       <c r="O19" t="n">
-        <v>15.56682191986587</v>
+        <v>15.53908290089049</v>
       </c>
       <c r="P19" t="n">
-        <v>388.5010840004298</v>
+        <v>388.5622070016692</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -27143,28 +27261,28 @@
         <v>0.0308</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5353580715931887</v>
+        <v>0.5373267053496792</v>
       </c>
       <c r="J20" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K20" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1116586511494995</v>
+        <v>0.1134544037051983</v>
       </c>
       <c r="M20" t="n">
-        <v>9.4510049988739</v>
+        <v>9.415524787373913</v>
       </c>
       <c r="N20" t="n">
-        <v>141.0819302732314</v>
+        <v>140.4291223193705</v>
       </c>
       <c r="O20" t="n">
-        <v>11.87779147288044</v>
+        <v>11.85027941946394</v>
       </c>
       <c r="P20" t="n">
-        <v>382.738006830314</v>
+        <v>382.7200840309926</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -27221,28 +27339,28 @@
         <v>0.0381</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5196049542367555</v>
+        <v>0.5208073494098626</v>
       </c>
       <c r="J21" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K21" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1262596613748875</v>
+        <v>0.1279548461274383</v>
       </c>
       <c r="M21" t="n">
-        <v>8.319337030432729</v>
+        <v>8.284664270449779</v>
       </c>
       <c r="N21" t="n">
-        <v>116.48183519713</v>
+        <v>115.9220363279992</v>
       </c>
       <c r="O21" t="n">
-        <v>10.79267507141441</v>
+        <v>10.76670963330948</v>
       </c>
       <c r="P21" t="n">
-        <v>382.3082384970518</v>
+        <v>382.2972692556529</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -27299,28 +27417,28 @@
         <v>0.0421</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3799322772593411</v>
+        <v>0.379915300119175</v>
       </c>
       <c r="J22" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K22" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0755262935555332</v>
+        <v>0.07626627433777566</v>
       </c>
       <c r="M22" t="n">
-        <v>8.161091511219286</v>
+        <v>8.121754501904464</v>
       </c>
       <c r="N22" t="n">
-        <v>112.2169078085661</v>
+        <v>111.6747988640491</v>
       </c>
       <c r="O22" t="n">
-        <v>10.59324821801916</v>
+        <v>10.56762976565933</v>
       </c>
       <c r="P22" t="n">
-        <v>383.4572306564444</v>
+        <v>383.4573827625662</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -27377,28 +27495,28 @@
         <v>0.0526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3363694778028348</v>
+        <v>0.3340959833698048</v>
       </c>
       <c r="J23" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K23" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05781007976851993</v>
+        <v>0.05764779587652469</v>
       </c>
       <c r="M23" t="n">
-        <v>8.157528473950121</v>
+        <v>8.130956070182274</v>
       </c>
       <c r="N23" t="n">
-        <v>113.6034338383262</v>
+        <v>113.0944229125383</v>
       </c>
       <c r="O23" t="n">
-        <v>10.6584911614321</v>
+        <v>10.63458616555145</v>
       </c>
       <c r="P23" t="n">
-        <v>381.4633115768759</v>
+        <v>381.4839895802795</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -27455,28 +27573,28 @@
         <v>0.0468</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5942084258775993</v>
+        <v>0.5885788259780714</v>
       </c>
       <c r="J24" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K24" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1798268709458274</v>
+        <v>0.178353488790513</v>
       </c>
       <c r="M24" t="n">
-        <v>8.055865144902913</v>
+        <v>8.045039114518044</v>
       </c>
       <c r="N24" t="n">
-        <v>99.20920567706635</v>
+        <v>98.91924924240811</v>
       </c>
       <c r="O24" t="n">
-        <v>9.960381803779731</v>
+        <v>9.945815665012503</v>
       </c>
       <c r="P24" t="n">
-        <v>376.7247528719469</v>
+        <v>376.7759554982619</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -27533,28 +27651,28 @@
         <v>0.0457</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5180083178856082</v>
+        <v>0.5075994118776429</v>
       </c>
       <c r="J25" t="n">
+        <v>213</v>
+      </c>
+      <c r="K25" t="n">
         <v>212</v>
       </c>
-      <c r="K25" t="n">
-        <v>211</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1473363169593352</v>
+        <v>0.1428337996522008</v>
       </c>
       <c r="M25" t="n">
-        <v>8.235283314243006</v>
+        <v>8.247129756910088</v>
       </c>
       <c r="N25" t="n">
-        <v>96.92645339999419</v>
+        <v>97.09696406321584</v>
       </c>
       <c r="O25" t="n">
-        <v>9.845123330867633</v>
+        <v>9.853779176702503</v>
       </c>
       <c r="P25" t="n">
-        <v>376.0735772876399</v>
+        <v>376.1671126655819</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -27611,28 +27729,28 @@
         <v>0.0465</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3585993278869169</v>
+        <v>0.3505792290195413</v>
       </c>
       <c r="J26" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K26" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07713495698826356</v>
+        <v>0.07444717530767697</v>
       </c>
       <c r="M26" t="n">
-        <v>8.233911474846183</v>
+        <v>8.23107972698133</v>
       </c>
       <c r="N26" t="n">
-        <v>96.4116188140346</v>
+        <v>96.32948379833455</v>
       </c>
       <c r="O26" t="n">
-        <v>9.818941837796709</v>
+        <v>9.814758468670258</v>
       </c>
       <c r="P26" t="n">
-        <v>377.083570789273</v>
+        <v>377.1555428694093</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -27689,28 +27807,28 @@
         <v>0.0476</v>
       </c>
       <c r="I27" t="n">
-        <v>0.05536081120471528</v>
+        <v>0.05188578326192432</v>
       </c>
       <c r="J27" t="n">
+        <v>213</v>
+      </c>
+      <c r="K27" t="n">
         <v>212</v>
       </c>
-      <c r="K27" t="n">
-        <v>211</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.00178975937860526</v>
+        <v>0.001588436802517523</v>
       </c>
       <c r="M27" t="n">
-        <v>8.667712857442453</v>
+        <v>8.64154014011552</v>
       </c>
       <c r="N27" t="n">
-        <v>106.6923210665676</v>
+        <v>106.2590180282768</v>
       </c>
       <c r="O27" t="n">
-        <v>10.32919750351244</v>
+        <v>10.30820149338752</v>
       </c>
       <c r="P27" t="n">
-        <v>379.7009675590279</v>
+        <v>379.7321944767982</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -27767,28 +27885,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.04410771557141707</v>
+        <v>-0.04486848136532733</v>
       </c>
       <c r="J28" t="n">
+        <v>213</v>
+      </c>
+      <c r="K28" t="n">
         <v>212</v>
       </c>
-      <c r="K28" t="n">
-        <v>211</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.001003448641334725</v>
+        <v>0.001049538824868135</v>
       </c>
       <c r="M28" t="n">
-        <v>9.027589684819251</v>
+        <v>8.989123850494705</v>
       </c>
       <c r="N28" t="n">
-        <v>120.8923637154922</v>
+        <v>120.3254698550969</v>
       </c>
       <c r="O28" t="n">
-        <v>10.99510635307782</v>
+        <v>10.96929668917278</v>
       </c>
       <c r="P28" t="n">
-        <v>376.3916604549036</v>
+        <v>376.3984967656555</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -27845,28 +27963,28 @@
         <v>0.045</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.08294437000008945</v>
+        <v>-0.07622526662685714</v>
       </c>
       <c r="J29" t="n">
+        <v>213</v>
+      </c>
+      <c r="K29" t="n">
         <v>212</v>
       </c>
-      <c r="K29" t="n">
-        <v>211</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.002767991601390518</v>
+        <v>0.002359996000432241</v>
       </c>
       <c r="M29" t="n">
-        <v>10.19906838217221</v>
+        <v>10.18357201762537</v>
       </c>
       <c r="N29" t="n">
-        <v>154.705646832762</v>
+        <v>154.2374637116415</v>
       </c>
       <c r="O29" t="n">
-        <v>12.43807247256431</v>
+        <v>12.41923764615371</v>
       </c>
       <c r="P29" t="n">
-        <v>370.2577256552719</v>
+        <v>370.1973471800541</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -27923,28 +28041,28 @@
         <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1392221683471474</v>
+        <v>-0.1244284166064732</v>
       </c>
       <c r="J30" t="n">
+        <v>213</v>
+      </c>
+      <c r="K30" t="n">
         <v>212</v>
       </c>
-      <c r="K30" t="n">
-        <v>211</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.005398864986652652</v>
+        <v>0.004339042142993965</v>
       </c>
       <c r="M30" t="n">
-        <v>12.39665197439314</v>
+        <v>12.42751091953521</v>
       </c>
       <c r="N30" t="n">
-        <v>222.8764436301142</v>
+        <v>223.0931014209653</v>
       </c>
       <c r="O30" t="n">
-        <v>14.92904697661958</v>
+        <v>14.93630146391553</v>
       </c>
       <c r="P30" t="n">
-        <v>360.5884899697879</v>
+        <v>360.4555519685048</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -28001,28 +28119,28 @@
         <v>0.0481</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3470530022100317</v>
+        <v>-0.332447485688906</v>
       </c>
       <c r="J31" t="n">
+        <v>213</v>
+      </c>
+      <c r="K31" t="n">
         <v>212</v>
       </c>
-      <c r="K31" t="n">
-        <v>211</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.04121278333753453</v>
+        <v>0.03808131107222856</v>
       </c>
       <c r="M31" t="n">
-        <v>10.8294914324313</v>
+        <v>10.85103884225522</v>
       </c>
       <c r="N31" t="n">
-        <v>174.8971767623095</v>
+        <v>175.3080901226395</v>
       </c>
       <c r="O31" t="n">
-        <v>13.22486963120278</v>
+        <v>13.24039614674121</v>
       </c>
       <c r="P31" t="n">
-        <v>352.9834617731738</v>
+        <v>352.8522152707271</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -28079,28 +28197,28 @@
         <v>0.0455</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3807846149159251</v>
+        <v>-0.3785747056940153</v>
       </c>
       <c r="J32" t="n">
+        <v>213</v>
+      </c>
+      <c r="K32" t="n">
         <v>212</v>
       </c>
-      <c r="K32" t="n">
-        <v>211</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.0887824102500635</v>
+        <v>0.08868808512480741</v>
       </c>
       <c r="M32" t="n">
-        <v>7.934147166953283</v>
+        <v>7.907750896416745</v>
       </c>
       <c r="N32" t="n">
-        <v>92.88698109882679</v>
+        <v>92.47712922386101</v>
       </c>
       <c r="O32" t="n">
-        <v>9.637789222577281</v>
+        <v>9.616502962296689</v>
       </c>
       <c r="P32" t="n">
-        <v>351.8708756292932</v>
+        <v>351.851017183638</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -28157,28 +28275,28 @@
         <v>0.0372</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8096004099761117</v>
+        <v>-0.8103910547570859</v>
       </c>
       <c r="J33" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K33" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L33" t="n">
-        <v>0.219225471629421</v>
+        <v>0.221404421539146</v>
       </c>
       <c r="M33" t="n">
-        <v>9.607729873694856</v>
+        <v>9.566876787266269</v>
       </c>
       <c r="N33" t="n">
-        <v>149.2263841223837</v>
+        <v>148.509200297336</v>
       </c>
       <c r="O33" t="n">
-        <v>12.21582515110558</v>
+        <v>12.18643509387942</v>
       </c>
       <c r="P33" t="n">
-        <v>349.0493468646065</v>
+        <v>349.0563576517261</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -28216,7 +28334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH213"/>
+  <dimension ref="A1:AH214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64591,6 +64709,178 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>-35.29140108650909,173.1596762205659</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>-35.290893086617785,173.15901640015647</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>-35.29036550678734,173.15838649220282</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-35.289820484847176,173.1577832302197</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-35.28924435229436,173.15722750046604</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-35.2886642219714,173.15667787329747</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-35.28808099392412,173.15613297340346</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-35.28751812416672,173.15555695886732</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-35.28693050066307,173.1550187630549</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-35.286344729438945,173.15447773067342</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-35.285764804121506,173.15392775926858</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-35.28518774347136,173.15337340431685</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-35.28461143744846,173.15281949578423</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-35.28405092722876,173.15224929386187</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>-35.28346574772571,173.15171410001267</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>-35.282805174560394,173.15128275557785</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>-35.28211952344741,173.150888479605</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>-35.28154604502269,173.15032836383477</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>-35.28105237634015,173.1496502530097</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>-35.280476881559345,173.14909310648682</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>-35.27988898924683,173.14855428244294</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>-35.279290937289645,173.14803047240753</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>-35.2787153736756,173.14747341016013</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>-35.27810337155472,173.14697021210668</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>-35.27753468561937,173.14640297037502</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>-35.27696961891979,173.14583553551816</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>-35.27640962638111,173.14526201865496</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>-35.27588136856589,173.1446405081131</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>-35.27533194627962,173.14404494153777</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>-35.27471400637187,173.14353894995799</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>-35.2740801958079,173.14305370284154</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>-35.27343684948438,173.14258091788196</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0067/nzd0067.xlsx
+++ b/data/nzd0067/nzd0067.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH214"/>
+  <dimension ref="A1:AH216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23425,7 +23425,7 @@
         <v>387.69</v>
       </c>
       <c r="S214" t="n">
-        <v>386.35</v>
+        <v>390.45</v>
       </c>
       <c r="T214" t="n">
         <v>398.92</v>
@@ -23470,6 +23470,222 @@
         <v>326.98</v>
       </c>
       <c r="AH214" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>412.12</v>
+      </c>
+      <c r="C215" t="n">
+        <v>423.28</v>
+      </c>
+      <c r="D215" t="n">
+        <v>430.79</v>
+      </c>
+      <c r="E215" t="n">
+        <v>436.39</v>
+      </c>
+      <c r="F215" t="n">
+        <v>435.84</v>
+      </c>
+      <c r="G215" t="n">
+        <v>429.64</v>
+      </c>
+      <c r="H215" t="n">
+        <v>429.42</v>
+      </c>
+      <c r="I215" t="n">
+        <v>431.51</v>
+      </c>
+      <c r="J215" t="n">
+        <v>431.24</v>
+      </c>
+      <c r="K215" t="n">
+        <v>430.65</v>
+      </c>
+      <c r="L215" t="n">
+        <v>430.18</v>
+      </c>
+      <c r="M215" t="n">
+        <v>429.55</v>
+      </c>
+      <c r="N215" t="n">
+        <v>428.29</v>
+      </c>
+      <c r="O215" t="n">
+        <v>428.63</v>
+      </c>
+      <c r="P215" t="n">
+        <v>424.24</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>407.62</v>
+      </c>
+      <c r="R215" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="S215" t="n">
+        <v>392.63</v>
+      </c>
+      <c r="T215" t="n">
+        <v>400.52</v>
+      </c>
+      <c r="U215" t="n">
+        <v>399.77</v>
+      </c>
+      <c r="V215" t="n">
+        <v>394.76</v>
+      </c>
+      <c r="W215" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="X215" t="n">
+        <v>384.57</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>376.46</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>376.16</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>374.53</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:18:04+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>413.11</v>
+      </c>
+      <c r="C216" t="n">
+        <v>425.53</v>
+      </c>
+      <c r="D216" t="n">
+        <v>433.46</v>
+      </c>
+      <c r="E216" t="n">
+        <v>438.31</v>
+      </c>
+      <c r="F216" t="n">
+        <v>436.6</v>
+      </c>
+      <c r="G216" t="n">
+        <v>429.9</v>
+      </c>
+      <c r="H216" t="n">
+        <v>429.03</v>
+      </c>
+      <c r="I216" t="n">
+        <v>430.86</v>
+      </c>
+      <c r="J216" t="n">
+        <v>431.25</v>
+      </c>
+      <c r="K216" t="n">
+        <v>432.08</v>
+      </c>
+      <c r="L216" t="n">
+        <v>432</v>
+      </c>
+      <c r="M216" t="n">
+        <v>431.27</v>
+      </c>
+      <c r="N216" t="n">
+        <v>429.71</v>
+      </c>
+      <c r="O216" t="n">
+        <v>429.68</v>
+      </c>
+      <c r="P216" t="n">
+        <v>425.13</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>410.06</v>
+      </c>
+      <c r="R216" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="S216" t="n">
+        <v>395.66</v>
+      </c>
+      <c r="T216" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="U216" t="n">
+        <v>402.34</v>
+      </c>
+      <c r="V216" t="n">
+        <v>397.75</v>
+      </c>
+      <c r="W216" t="n">
+        <v>389.62</v>
+      </c>
+      <c r="X216" t="n">
+        <v>385.44</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>376.16</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>374.53</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="AH216" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23486,7 +23702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25689,6 +25905,26 @@
       </c>
       <c r="B220" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -25857,28 +26093,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1740652560191204</v>
+        <v>0.1663003234709572</v>
       </c>
       <c r="J2" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K2" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01459584677419246</v>
+        <v>0.01360265339320477</v>
       </c>
       <c r="M2" t="n">
-        <v>8.98055213591128</v>
+        <v>8.936578674882515</v>
       </c>
       <c r="N2" t="n">
-        <v>128.1836166542582</v>
+        <v>127.1549725867803</v>
       </c>
       <c r="O2" t="n">
-        <v>11.3218203772299</v>
+        <v>11.27630136998743</v>
       </c>
       <c r="P2" t="n">
-        <v>412.4605323280388</v>
+        <v>412.5309245111409</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25935,28 +26171,28 @@
         <v>0.0361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1611025186161366</v>
+        <v>0.1577993557316158</v>
       </c>
       <c r="J3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01352021100017819</v>
+        <v>0.01324785459838473</v>
       </c>
       <c r="M3" t="n">
-        <v>8.235223649331399</v>
+        <v>8.175387587596212</v>
       </c>
       <c r="N3" t="n">
-        <v>118.0857752543805</v>
+        <v>117.0053718725254</v>
       </c>
       <c r="O3" t="n">
-        <v>10.86672790008016</v>
+        <v>10.81690213843711</v>
       </c>
       <c r="P3" t="n">
-        <v>422.0450522343145</v>
+        <v>422.0752454969704</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26013,28 +26249,28 @@
         <v>0.0434</v>
       </c>
       <c r="I4" t="n">
-        <v>0.268082584850574</v>
+        <v>0.2663267738575803</v>
       </c>
       <c r="J4" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K4" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02590448718482952</v>
+        <v>0.02610572119074717</v>
       </c>
       <c r="M4" t="n">
-        <v>9.842721132366252</v>
+        <v>9.761431224254205</v>
       </c>
       <c r="N4" t="n">
-        <v>166.0846380882162</v>
+        <v>164.5136727678472</v>
       </c>
       <c r="O4" t="n">
-        <v>12.88738290298756</v>
+        <v>12.82628834729078</v>
       </c>
       <c r="P4" t="n">
-        <v>426.063361882113</v>
+        <v>426.0796606076383</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26091,28 +26327,28 @@
         <v>0.0469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3240768640869354</v>
+        <v>0.3260134395685946</v>
       </c>
       <c r="J5" t="n">
+        <v>215</v>
+      </c>
+      <c r="K5" t="n">
         <v>213</v>
       </c>
-      <c r="K5" t="n">
-        <v>211</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.03834472011054535</v>
+        <v>0.0395797388267527</v>
       </c>
       <c r="M5" t="n">
-        <v>9.982695335264021</v>
+        <v>9.89762825499229</v>
       </c>
       <c r="N5" t="n">
-        <v>165.1727153176875</v>
+        <v>163.6414978859202</v>
       </c>
       <c r="O5" t="n">
-        <v>12.85195375488441</v>
+        <v>12.7922436611378</v>
       </c>
       <c r="P5" t="n">
-        <v>427.7425758999436</v>
+        <v>427.7250462066957</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26169,28 +26405,28 @@
         <v>0.045</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4634026379828091</v>
+        <v>0.463080245855793</v>
       </c>
       <c r="J6" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K6" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07317634045453425</v>
+        <v>0.07452943956960423</v>
       </c>
       <c r="M6" t="n">
-        <v>9.924878012226019</v>
+        <v>9.833848338912988</v>
       </c>
       <c r="N6" t="n">
-        <v>168.3750245389101</v>
+        <v>166.7731043123883</v>
       </c>
       <c r="O6" t="n">
-        <v>12.97594021791524</v>
+        <v>12.9140661417072</v>
       </c>
       <c r="P6" t="n">
-        <v>424.2395255989335</v>
+        <v>424.2424901157124</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26247,28 +26483,28 @@
         <v>0.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5892742843939653</v>
+        <v>0.580574877089688</v>
       </c>
       <c r="J7" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K7" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L7" t="n">
-        <v>0.132581707815413</v>
+        <v>0.1314145081161627</v>
       </c>
       <c r="M7" t="n">
-        <v>9.620021325393601</v>
+        <v>9.58156865589509</v>
       </c>
       <c r="N7" t="n">
-        <v>143.6876818298167</v>
+        <v>142.5777941868819</v>
       </c>
       <c r="O7" t="n">
-        <v>11.98697967921097</v>
+        <v>11.94059438164122</v>
       </c>
       <c r="P7" t="n">
-        <v>419.3135047462937</v>
+        <v>419.391352538471</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26325,28 +26561,28 @@
         <v>0.0427</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6679098109444517</v>
+        <v>0.6594728717132173</v>
       </c>
       <c r="J8" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K8" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1726433892376631</v>
+        <v>0.1718012813234294</v>
       </c>
       <c r="M8" t="n">
-        <v>9.296066250457304</v>
+        <v>9.24812624330446</v>
       </c>
       <c r="N8" t="n">
-        <v>135.7467440798641</v>
+        <v>134.692774529218</v>
       </c>
       <c r="O8" t="n">
-        <v>11.65104047198636</v>
+        <v>11.60572162897327</v>
       </c>
       <c r="P8" t="n">
-        <v>416.5584737312122</v>
+        <v>416.6338725004384</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26403,28 +26639,28 @@
         <v>0.0432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.723009822488593</v>
+        <v>0.7197768224474935</v>
       </c>
       <c r="J9" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K9" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1920988629561414</v>
+        <v>0.1939606692204521</v>
       </c>
       <c r="M9" t="n">
-        <v>9.226446096695975</v>
+        <v>9.158004809824485</v>
       </c>
       <c r="N9" t="n">
-        <v>139.046932562077</v>
+        <v>137.7857904436403</v>
       </c>
       <c r="O9" t="n">
-        <v>11.79181633854925</v>
+        <v>11.73821921944041</v>
       </c>
       <c r="P9" t="n">
-        <v>414.0671492805477</v>
+        <v>414.0960834494182</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26481,28 +26717,28 @@
         <v>0.0369</v>
       </c>
       <c r="I10" t="n">
-        <v>0.859895691278071</v>
+        <v>0.8578028877288034</v>
       </c>
       <c r="J10" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K10" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2563765932780021</v>
+        <v>0.2594732439751076</v>
       </c>
       <c r="M10" t="n">
-        <v>9.233417251394238</v>
+        <v>9.159525977126517</v>
       </c>
       <c r="N10" t="n">
-        <v>135.6456332085584</v>
+        <v>134.3969266585636</v>
       </c>
       <c r="O10" t="n">
-        <v>11.64670052884328</v>
+        <v>11.59296884575145</v>
       </c>
       <c r="P10" t="n">
-        <v>409.8752175560203</v>
+        <v>409.8939455829814</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26559,28 +26795,28 @@
         <v>0.0378</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8576764952660551</v>
+        <v>0.8580133532502836</v>
       </c>
       <c r="J11" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K11" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2314782705408226</v>
+        <v>0.2353976730083598</v>
       </c>
       <c r="M11" t="n">
-        <v>9.757128523028834</v>
+        <v>9.673157391536082</v>
       </c>
       <c r="N11" t="n">
-        <v>154.4658688851912</v>
+        <v>153.0339190279378</v>
       </c>
       <c r="O11" t="n">
-        <v>12.42842986403315</v>
+        <v>12.37068789631109</v>
       </c>
       <c r="P11" t="n">
-        <v>408.6562090675727</v>
+        <v>408.6531886068926</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26637,28 +26873,28 @@
         <v>0.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7380878234897567</v>
+        <v>0.7429157547333846</v>
       </c>
       <c r="J12" t="n">
+        <v>215</v>
+      </c>
+      <c r="K12" t="n">
         <v>213</v>
       </c>
-      <c r="K12" t="n">
-        <v>211</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1789990393358929</v>
+        <v>0.1840284863000354</v>
       </c>
       <c r="M12" t="n">
-        <v>9.90888556090831</v>
+        <v>9.841730821466856</v>
       </c>
       <c r="N12" t="n">
-        <v>154.8735248394379</v>
+        <v>153.4948078392496</v>
       </c>
       <c r="O12" t="n">
-        <v>12.44481919673556</v>
+        <v>12.38930215303709</v>
       </c>
       <c r="P12" t="n">
-        <v>408.9814281819231</v>
+        <v>408.9373466633339</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26715,28 +26951,28 @@
         <v>0.0375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6844571771487208</v>
+        <v>0.6960577412410848</v>
       </c>
       <c r="J13" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K13" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1528905377097909</v>
+        <v>0.1597808905401069</v>
       </c>
       <c r="M13" t="n">
-        <v>10.18216336529799</v>
+        <v>10.13934097836666</v>
       </c>
       <c r="N13" t="n">
-        <v>164.168972864887</v>
+        <v>163.051353967225</v>
       </c>
       <c r="O13" t="n">
-        <v>12.81284405840042</v>
+        <v>12.7691563529947</v>
       </c>
       <c r="P13" t="n">
-        <v>405.7606612010512</v>
+        <v>405.6568433471447</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26793,28 +27029,28 @@
         <v>0.0353</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6892540083443958</v>
+        <v>0.7006804689207297</v>
       </c>
       <c r="J14" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K14" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1593569790865774</v>
+        <v>0.1663803724878542</v>
       </c>
       <c r="M14" t="n">
-        <v>9.973942601879859</v>
+        <v>9.939577626750305</v>
       </c>
       <c r="N14" t="n">
-        <v>158.5034490220121</v>
+        <v>157.4243901844069</v>
       </c>
       <c r="O14" t="n">
-        <v>12.58981528943186</v>
+        <v>12.54688766923523</v>
       </c>
       <c r="P14" t="n">
-        <v>404.3264507012636</v>
+        <v>404.2241921331714</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26871,28 +27107,28 @@
         <v>0.0359</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6097958051334057</v>
+        <v>0.6255775242804186</v>
       </c>
       <c r="J15" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K15" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1305087131157694</v>
+        <v>0.1383666918236016</v>
       </c>
       <c r="M15" t="n">
-        <v>9.645184888787405</v>
+        <v>9.623204715283476</v>
       </c>
       <c r="N15" t="n">
-        <v>155.0607195617565</v>
+        <v>154.349049191198</v>
       </c>
       <c r="O15" t="n">
-        <v>12.4523379154983</v>
+        <v>12.423729278731</v>
       </c>
       <c r="P15" t="n">
-        <v>404.1415483201898</v>
+        <v>403.9988584497844</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26949,28 +27185,28 @@
         <v>0.0309</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3621510473795633</v>
+        <v>0.3830946353768993</v>
       </c>
       <c r="J16" t="n">
+        <v>215</v>
+      </c>
+      <c r="K16" t="n">
         <v>213</v>
       </c>
-      <c r="K16" t="n">
-        <v>211</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.05114657594754979</v>
+        <v>0.05757669304507762</v>
       </c>
       <c r="M16" t="n">
-        <v>9.888856556826903</v>
+        <v>9.886416196543387</v>
       </c>
       <c r="N16" t="n">
-        <v>150.8100180068756</v>
+        <v>150.6732135260629</v>
       </c>
       <c r="O16" t="n">
-        <v>12.28047303677165</v>
+        <v>12.2749017725627</v>
       </c>
       <c r="P16" t="n">
-        <v>403.3332715573886</v>
+        <v>403.1420759722836</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27027,28 +27263,28 @@
         <v>0.0256</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.08185795075722485</v>
+        <v>-0.06510116932272617</v>
       </c>
       <c r="J17" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K17" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L17" t="n">
-        <v>0.002634678557091652</v>
+        <v>0.001694789511554773</v>
       </c>
       <c r="M17" t="n">
-        <v>10.36968432246348</v>
+        <v>10.35073066837807</v>
       </c>
       <c r="N17" t="n">
-        <v>160.8801435825594</v>
+        <v>160.2285053273043</v>
       </c>
       <c r="O17" t="n">
-        <v>12.68385365662027</v>
+        <v>12.65813988417352</v>
       </c>
       <c r="P17" t="n">
-        <v>401.3719641922074</v>
+        <v>401.2224732582226</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27105,28 +27341,28 @@
         <v>0.0209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2336546568369746</v>
+        <v>0.2249551685953967</v>
       </c>
       <c r="J18" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K18" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01275601155563155</v>
+        <v>0.01207456600025336</v>
       </c>
       <c r="M18" t="n">
-        <v>13.38088982477726</v>
+        <v>13.31117174649847</v>
       </c>
       <c r="N18" t="n">
-        <v>267.2379112884701</v>
+        <v>264.9785658553893</v>
       </c>
       <c r="O18" t="n">
-        <v>16.34741298458169</v>
+        <v>16.27816223826846</v>
       </c>
       <c r="P18" t="n">
-        <v>385.1791157583496</v>
+        <v>385.2569653680021</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27183,28 +27419,28 @@
         <v>0.0255</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2054837321641909</v>
+        <v>0.2093519005415048</v>
       </c>
       <c r="J19" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K19" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01093873021554004</v>
+        <v>0.01159867799764369</v>
       </c>
       <c r="M19" t="n">
-        <v>12.17443367609748</v>
+        <v>12.05483129730322</v>
       </c>
       <c r="N19" t="n">
-        <v>241.4630974007473</v>
+        <v>239.0258097395373</v>
       </c>
       <c r="O19" t="n">
-        <v>15.53908290089049</v>
+        <v>15.46045955783777</v>
       </c>
       <c r="P19" t="n">
-        <v>388.5622070016692</v>
+        <v>388.5277012350189</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -27261,28 +27497,28 @@
         <v>0.0308</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5373267053496792</v>
+        <v>0.5454360646703955</v>
       </c>
       <c r="J20" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K20" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1134544037051983</v>
+        <v>0.1185541289319038</v>
       </c>
       <c r="M20" t="n">
-        <v>9.415524787373913</v>
+        <v>9.365752421143133</v>
       </c>
       <c r="N20" t="n">
-        <v>140.4291223193705</v>
+        <v>139.2984606565507</v>
       </c>
       <c r="O20" t="n">
-        <v>11.85027941946394</v>
+        <v>11.80247688650779</v>
       </c>
       <c r="P20" t="n">
-        <v>382.7200840309926</v>
+        <v>382.645970607397</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -27339,28 +27575,28 @@
         <v>0.0381</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5208073494098626</v>
+        <v>0.5298333104213867</v>
       </c>
       <c r="J21" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K21" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1279548461274383</v>
+        <v>0.1340099026654678</v>
       </c>
       <c r="M21" t="n">
-        <v>8.284664270449779</v>
+        <v>8.248265495474467</v>
       </c>
       <c r="N21" t="n">
-        <v>115.9220363279992</v>
+        <v>115.0602415033437</v>
       </c>
       <c r="O21" t="n">
-        <v>10.76670963330948</v>
+        <v>10.72661370159958</v>
       </c>
       <c r="P21" t="n">
-        <v>382.2972692556529</v>
+        <v>382.2145995747593</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -27417,28 +27653,28 @@
         <v>0.0421</v>
       </c>
       <c r="I22" t="n">
-        <v>0.379915300119175</v>
+        <v>0.3848358894247537</v>
       </c>
       <c r="J22" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K22" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L22" t="n">
-        <v>0.07626627433777566</v>
+        <v>0.0795555284625904</v>
       </c>
       <c r="M22" t="n">
-        <v>8.121754501904464</v>
+        <v>8.071205289871989</v>
       </c>
       <c r="N22" t="n">
-        <v>111.6747988640491</v>
+        <v>110.7014095068369</v>
       </c>
       <c r="O22" t="n">
-        <v>10.56762976565933</v>
+        <v>10.52147373264967</v>
       </c>
       <c r="P22" t="n">
-        <v>383.4573827625662</v>
+        <v>383.4131117100288</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -27495,28 +27731,28 @@
         <v>0.0526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3340959833698048</v>
+        <v>0.3314102146428237</v>
       </c>
       <c r="J23" t="n">
+        <v>215</v>
+      </c>
+      <c r="K23" t="n">
         <v>213</v>
       </c>
-      <c r="K23" t="n">
-        <v>211</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.05764779587652469</v>
+        <v>0.05791518639855542</v>
       </c>
       <c r="M23" t="n">
-        <v>8.130956070182274</v>
+        <v>8.068669097025346</v>
       </c>
       <c r="N23" t="n">
-        <v>113.0944229125383</v>
+        <v>112.0608555503766</v>
       </c>
       <c r="O23" t="n">
-        <v>10.63458616555145</v>
+        <v>10.58588000831186</v>
       </c>
       <c r="P23" t="n">
-        <v>381.4839895802795</v>
+        <v>381.5084999842014</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -27573,28 +27809,28 @@
         <v>0.0468</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5885788259780714</v>
+        <v>0.5758130910803548</v>
       </c>
       <c r="J24" t="n">
+        <v>215</v>
+      </c>
+      <c r="K24" t="n">
         <v>213</v>
       </c>
-      <c r="K24" t="n">
-        <v>211</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.178353488790513</v>
+        <v>0.1743738136773573</v>
       </c>
       <c r="M24" t="n">
-        <v>8.045039114518044</v>
+        <v>8.030511586535312</v>
       </c>
       <c r="N24" t="n">
-        <v>98.91924924240811</v>
+        <v>98.4668105580657</v>
       </c>
       <c r="O24" t="n">
-        <v>9.945815665012503</v>
+        <v>9.923044419837376</v>
       </c>
       <c r="P24" t="n">
-        <v>376.7759554982619</v>
+        <v>376.8924888028884</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -27651,28 +27887,28 @@
         <v>0.0457</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5075994118776429</v>
+        <v>0.4855765898691817</v>
       </c>
       <c r="J25" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K25" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1428337996522008</v>
+        <v>0.1330407320911735</v>
       </c>
       <c r="M25" t="n">
-        <v>8.247129756910088</v>
+        <v>8.2781024305977</v>
       </c>
       <c r="N25" t="n">
-        <v>97.09696406321584</v>
+        <v>97.63021468632138</v>
       </c>
       <c r="O25" t="n">
-        <v>9.853779176702503</v>
+        <v>9.880800305963145</v>
       </c>
       <c r="P25" t="n">
-        <v>376.1671126655819</v>
+        <v>376.365749525563</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -27729,28 +27965,28 @@
         <v>0.0465</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3505792290195413</v>
+        <v>0.3327541474479139</v>
       </c>
       <c r="J26" t="n">
+        <v>215</v>
+      </c>
+      <c r="K26" t="n">
         <v>213</v>
       </c>
-      <c r="K26" t="n">
-        <v>211</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.07444717530767697</v>
+        <v>0.06828101587307212</v>
       </c>
       <c r="M26" t="n">
-        <v>8.23107972698133</v>
+        <v>8.235249571367349</v>
       </c>
       <c r="N26" t="n">
-        <v>96.32948379833455</v>
+        <v>96.37298855656776</v>
       </c>
       <c r="O26" t="n">
-        <v>9.814758468670258</v>
+        <v>9.816974511353678</v>
       </c>
       <c r="P26" t="n">
-        <v>377.1555428694093</v>
+        <v>377.3161085809655</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -27807,28 +28043,28 @@
         <v>0.0476</v>
       </c>
       <c r="I27" t="n">
-        <v>0.05188578326192432</v>
+        <v>0.0444361254953959</v>
       </c>
       <c r="J27" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K27" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001588436802517523</v>
+        <v>0.001188622357656377</v>
       </c>
       <c r="M27" t="n">
-        <v>8.64154014011552</v>
+        <v>8.592256290706818</v>
       </c>
       <c r="N27" t="n">
-        <v>106.2590180282768</v>
+        <v>105.4305932438021</v>
       </c>
       <c r="O27" t="n">
-        <v>10.30820149338752</v>
+        <v>10.2679400681832</v>
       </c>
       <c r="P27" t="n">
-        <v>379.7321944767982</v>
+        <v>379.7993885914494</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -27885,28 +28121,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.04486848136532733</v>
+        <v>-0.04607573047296828</v>
       </c>
       <c r="J28" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K28" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L28" t="n">
-        <v>0.001049538824868135</v>
+        <v>0.001130349024805688</v>
       </c>
       <c r="M28" t="n">
-        <v>8.989123850494705</v>
+        <v>8.911543556014141</v>
       </c>
       <c r="N28" t="n">
-        <v>120.3254698550969</v>
+        <v>119.2052567386924</v>
       </c>
       <c r="O28" t="n">
-        <v>10.96929668917278</v>
+        <v>10.91811598851617</v>
       </c>
       <c r="P28" t="n">
-        <v>376.3984967656555</v>
+        <v>376.4093858561426</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -27963,28 +28199,28 @@
         <v>0.045</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.07622526662685714</v>
+        <v>-0.06311341171586292</v>
       </c>
       <c r="J29" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K29" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002359996000432241</v>
+        <v>0.001648247047674523</v>
       </c>
       <c r="M29" t="n">
-        <v>10.18357201762537</v>
+        <v>10.15323178093681</v>
       </c>
       <c r="N29" t="n">
-        <v>154.2374637116415</v>
+        <v>153.3060479854085</v>
       </c>
       <c r="O29" t="n">
-        <v>12.41923764615371</v>
+        <v>12.38168195300657</v>
       </c>
       <c r="P29" t="n">
-        <v>370.1973471800541</v>
+        <v>370.0790814154801</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -28041,28 +28277,28 @@
         <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1244284166064732</v>
+        <v>-0.09648748241742588</v>
       </c>
       <c r="J30" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K30" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L30" t="n">
-        <v>0.004339042142993965</v>
+        <v>0.002641872206361251</v>
       </c>
       <c r="M30" t="n">
-        <v>12.42751091953521</v>
+        <v>12.47871922002312</v>
       </c>
       <c r="N30" t="n">
-        <v>223.0931014209653</v>
+        <v>223.3242941515331</v>
       </c>
       <c r="O30" t="n">
-        <v>14.93630146391553</v>
+        <v>14.94403874966648</v>
       </c>
       <c r="P30" t="n">
-        <v>360.4555519685048</v>
+        <v>360.2035314938876</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -28119,28 +28355,28 @@
         <v>0.0481</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.332447485688906</v>
+        <v>-0.3048065118470649</v>
       </c>
       <c r="J31" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K31" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L31" t="n">
-        <v>0.03808131107222856</v>
+        <v>0.03246490846626582</v>
       </c>
       <c r="M31" t="n">
-        <v>10.85103884225522</v>
+        <v>10.88708211919259</v>
       </c>
       <c r="N31" t="n">
-        <v>175.3080901226395</v>
+        <v>175.936407506807</v>
       </c>
       <c r="O31" t="n">
-        <v>13.24039614674121</v>
+        <v>13.2641022126191</v>
       </c>
       <c r="P31" t="n">
-        <v>352.8522152707271</v>
+        <v>352.6029003462123</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -28197,28 +28433,28 @@
         <v>0.0455</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3785747056940153</v>
+        <v>-0.3731384840939117</v>
       </c>
       <c r="J32" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K32" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08868808512480741</v>
+        <v>0.08798800456442579</v>
       </c>
       <c r="M32" t="n">
-        <v>7.907750896416745</v>
+        <v>7.860559337561882</v>
       </c>
       <c r="N32" t="n">
-        <v>92.47712922386101</v>
+        <v>91.70053356760305</v>
       </c>
       <c r="O32" t="n">
-        <v>9.616502962296689</v>
+        <v>9.576039555453134</v>
       </c>
       <c r="P32" t="n">
-        <v>351.851017183638</v>
+        <v>351.8019837450141</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -28275,28 +28511,28 @@
         <v>0.0372</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8103910547570859</v>
+        <v>-0.8070737256836585</v>
       </c>
       <c r="J33" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K33" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L33" t="n">
-        <v>0.221404421539146</v>
+        <v>0.2236029847116464</v>
       </c>
       <c r="M33" t="n">
-        <v>9.566876787266269</v>
+        <v>9.487914011485854</v>
       </c>
       <c r="N33" t="n">
-        <v>148.509200297336</v>
+        <v>147.1215650568712</v>
       </c>
       <c r="O33" t="n">
-        <v>12.18643509387942</v>
+        <v>12.12936787540353</v>
       </c>
       <c r="P33" t="n">
-        <v>349.0563576517261</v>
+        <v>349.0268275953337</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -28334,7 +28570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH214"/>
+  <dimension ref="A1:AH216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64802,7 +65038,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>-35.28154604502269,173.15032836383477</t>
+          <t>-35.2815695703607,173.15029358446958</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
@@ -64876,6 +65112,350 @@
         </is>
       </c>
       <c r="AH214" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>-35.29140198652896,173.15967484530347</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>-35.290891567842976,173.15901872090595</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>-35.29036061298365,173.15839397015097</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-35.289818909837926,173.1577856369076</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-35.28924260854187,173.15723016500226</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-35.28863452205089,173.15672325615742</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-35.28806006907223,173.15616494755605</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-35.287498605647116,173.15558678410562</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-35.28692386327031,173.15502890531153</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-35.286347316885866,173.15447377692928</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-35.28577144145599,173.15391761709796</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-35.28519466201812,173.1533628324374</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-35.284614987335395,173.15281408704078</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>-35.28404870757223,173.15225262034852</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>-35.28346081309536,173.15172139531785</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>-35.28279966615084,173.1512908991241</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>-35.282111547747384,173.15090027070093</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>-35.28158207895097,173.15027509201843</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>-35.281061556908185,173.14963668060483</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>-35.28049145564811,173.14907156038046</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>-35.279896907420934,173.14854257634286</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>-35.27929145369036,173.14802970896983</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>-35.278706824410975,173.14748604924256</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>-35.278094478056495,173.14698336008004</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>-35.277526939703435,173.14641442179112</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>-35.27696703055095,173.1458392022709</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>-35.27641047870005,173.1452608830869</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>-35.275882045102385,173.14463962361302</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>-35.27533010118752,173.14404735380307</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>-35.27471234579404,173.1435411209863</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>-35.27408419348379,173.1430484763188</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>-35.27345345516885,173.14255920782546</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:18:04+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>-35.291407555401584,173.1596663358666</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>-35.29090422429832,173.15899938132412</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>-35.29037563189695,173.15837102058308</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-35.289829709900495,173.15776913390303</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-35.28924688354788,173.15722363259064</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-35.28863598454736,173.15672102139612</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-35.28805787533728,173.156168299684</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-35.287494949439456,173.15559237096423</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-35.28692391951942,173.1550288193602</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-35.28635536047001,173.1544614859405</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-35.28578167869902,173.15390197408584</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>-35.28520433673235,173.15334804899322</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>-35.28462298866693,173.15280189590308</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-35.28405468357039,173.15224366442257</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>-35.283465919863964,173.15171384552528</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>-35.28281366669073,173.15127020094192</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>-35.282111547747384,173.15090027070093</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>-35.281599464739145,173.1502493891984</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>-35.281071770288335,173.14962158130083</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>-35.28050620186786,173.14904975978467</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>-35.27991406346097,173.14851721311825</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>-35.279301609569785,173.14801469469296</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>-35.27871181626364,173.14747866937597</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>-35.27809941251375,173.14697606507582</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>-35.277526939703435,173.14641442179112</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>-35.27696703055095,173.1458392022709</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>-35.27641047870005,173.1452608830869</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>-35.275882045102385,173.14463962361302</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>-35.27533010118752,173.14404735380307</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>-35.27471234579404,173.1435411209863</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>-35.27408419348379,173.1430484763188</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>-35.27345345516885,173.14255920782546</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0067/nzd0067.xlsx
+++ b/data/nzd0067/nzd0067.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH216"/>
+  <dimension ref="A1:AH217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23638,7 +23638,7 @@
         <v>410.06</v>
       </c>
       <c r="R216" t="n">
-        <v>386.3</v>
+        <v>390.84</v>
       </c>
       <c r="S216" t="n">
         <v>395.66</v>
@@ -23688,6 +23688,114 @@
       <c r="AH216" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="C217" t="n">
+        <v>425.63</v>
+      </c>
+      <c r="D217" t="n">
+        <v>431.46</v>
+      </c>
+      <c r="E217" t="n">
+        <v>434.96</v>
+      </c>
+      <c r="F217" t="n">
+        <v>433.83</v>
+      </c>
+      <c r="G217" t="n">
+        <v>426.83</v>
+      </c>
+      <c r="H217" t="n">
+        <v>422.89</v>
+      </c>
+      <c r="I217" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="J217" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="K217" t="n">
+        <v>430.54</v>
+      </c>
+      <c r="L217" t="n">
+        <v>433.58</v>
+      </c>
+      <c r="M217" t="n">
+        <v>431.51</v>
+      </c>
+      <c r="N217" t="n">
+        <v>430.93</v>
+      </c>
+      <c r="O217" t="n">
+        <v>430.26</v>
+      </c>
+      <c r="P217" t="n">
+        <v>424.47</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>408.87</v>
+      </c>
+      <c r="R217" t="n">
+        <v>386.72</v>
+      </c>
+      <c r="S217" t="n">
+        <v>395.17</v>
+      </c>
+      <c r="T217" t="n">
+        <v>399.39</v>
+      </c>
+      <c r="U217" t="n">
+        <v>402.16</v>
+      </c>
+      <c r="V217" t="n">
+        <v>396.71</v>
+      </c>
+      <c r="W217" t="n">
+        <v>386.48</v>
+      </c>
+      <c r="X217" t="n">
+        <v>380.25</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>374.63</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>375.01</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>378.04</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>377.63</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>378.41</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>356.78</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>348.31</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23702,7 +23810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B222"/>
+  <dimension ref="A1:B223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25925,6 +26033,16 @@
       </c>
       <c r="B222" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -26093,28 +26211,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1663003234709572</v>
+        <v>0.163069054370548</v>
       </c>
       <c r="J2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01360265339320477</v>
+        <v>0.01321797348149134</v>
       </c>
       <c r="M2" t="n">
-        <v>8.936578674882515</v>
+        <v>8.911485696189347</v>
       </c>
       <c r="N2" t="n">
-        <v>127.1549725867803</v>
+        <v>126.6201595590426</v>
       </c>
       <c r="O2" t="n">
-        <v>11.27630136998743</v>
+        <v>11.25256235526125</v>
       </c>
       <c r="P2" t="n">
-        <v>412.5309245111409</v>
+        <v>412.5605188407648</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26171,28 +26289,28 @@
         <v>0.0361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1577993557316158</v>
+        <v>0.1572451650059616</v>
       </c>
       <c r="J3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01324785459838473</v>
+        <v>0.01329490780027287</v>
       </c>
       <c r="M3" t="n">
-        <v>8.175387587596212</v>
+        <v>8.139690172660861</v>
       </c>
       <c r="N3" t="n">
-        <v>117.0053718725254</v>
+        <v>116.4526651949139</v>
       </c>
       <c r="O3" t="n">
-        <v>10.81690213843711</v>
+        <v>10.79132360718156</v>
       </c>
       <c r="P3" t="n">
-        <v>422.0752454969704</v>
+        <v>422.0803648451133</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26249,28 +26367,28 @@
         <v>0.0434</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2663267738575803</v>
+        <v>0.2648244977526142</v>
       </c>
       <c r="J4" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K4" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02610572119074717</v>
+        <v>0.02608751436050516</v>
       </c>
       <c r="M4" t="n">
-        <v>9.761431224254205</v>
+        <v>9.723055944008268</v>
       </c>
       <c r="N4" t="n">
-        <v>164.5136727678472</v>
+        <v>163.7396742226505</v>
       </c>
       <c r="O4" t="n">
-        <v>12.82628834729078</v>
+        <v>12.79608042420219</v>
       </c>
       <c r="P4" t="n">
-        <v>426.0796606076383</v>
+        <v>426.0937580061784</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26327,28 +26445,28 @@
         <v>0.0469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3260134395685946</v>
+        <v>0.3247891278309323</v>
       </c>
       <c r="J5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395797388267527</v>
+        <v>0.03969646142521588</v>
       </c>
       <c r="M5" t="n">
-        <v>9.89762825499229</v>
+        <v>9.858786235378043</v>
       </c>
       <c r="N5" t="n">
-        <v>163.6414978859202</v>
+        <v>162.8857573007628</v>
       </c>
       <c r="O5" t="n">
-        <v>12.7922436611378</v>
+        <v>12.76267046118338</v>
       </c>
       <c r="P5" t="n">
-        <v>427.7250462066957</v>
+        <v>427.7362364813599</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26405,28 +26523,28 @@
         <v>0.045</v>
       </c>
       <c r="I6" t="n">
-        <v>0.463080245855793</v>
+        <v>0.4607060116119787</v>
       </c>
       <c r="J6" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K6" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07452943956960423</v>
+        <v>0.07454089111987738</v>
       </c>
       <c r="M6" t="n">
-        <v>9.833848338912988</v>
+        <v>9.799382243479888</v>
       </c>
       <c r="N6" t="n">
-        <v>166.7731043123883</v>
+        <v>166.015890060852</v>
       </c>
       <c r="O6" t="n">
-        <v>12.9140661417072</v>
+        <v>12.88471536592299</v>
       </c>
       <c r="P6" t="n">
-        <v>424.2424901157124</v>
+        <v>424.2645694521679</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26483,28 +26601,28 @@
         <v>0.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.580574877089688</v>
+        <v>0.5736864921727483</v>
       </c>
       <c r="J7" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K7" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1314145081161627</v>
+        <v>0.1296824433707875</v>
       </c>
       <c r="M7" t="n">
-        <v>9.58156865589509</v>
+        <v>9.577011102421171</v>
       </c>
       <c r="N7" t="n">
-        <v>142.5777941868819</v>
+        <v>142.2037157390247</v>
       </c>
       <c r="O7" t="n">
-        <v>11.94059438164122</v>
+        <v>11.92491994686022</v>
       </c>
       <c r="P7" t="n">
-        <v>419.391352538471</v>
+        <v>419.4536270694122</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26561,28 +26679,28 @@
         <v>0.0427</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6594728717132173</v>
+        <v>0.6497461088009191</v>
       </c>
       <c r="J8" t="n">
+        <v>216</v>
+      </c>
+      <c r="K8" t="n">
         <v>215</v>
       </c>
-      <c r="K8" t="n">
-        <v>214</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1718012813234294</v>
+        <v>0.1685000496010589</v>
       </c>
       <c r="M8" t="n">
-        <v>9.24812624330446</v>
+        <v>9.249530513842204</v>
       </c>
       <c r="N8" t="n">
-        <v>134.692774529218</v>
+        <v>134.6397539623289</v>
       </c>
       <c r="O8" t="n">
-        <v>11.60572162897327</v>
+        <v>11.60343716156247</v>
       </c>
       <c r="P8" t="n">
-        <v>416.6338725004384</v>
+        <v>416.7216943563801</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26639,28 +26757,28 @@
         <v>0.0432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7197768224474935</v>
+        <v>0.7104876767756991</v>
       </c>
       <c r="J9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1939606692204521</v>
+        <v>0.1909859112047467</v>
       </c>
       <c r="M9" t="n">
-        <v>9.158004809824485</v>
+        <v>9.164462020237258</v>
       </c>
       <c r="N9" t="n">
-        <v>137.7857904436403</v>
+        <v>137.6679955217183</v>
       </c>
       <c r="O9" t="n">
-        <v>11.73821921944041</v>
+        <v>11.73320056598873</v>
       </c>
       <c r="P9" t="n">
-        <v>414.0960834494182</v>
+        <v>414.18006208832</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26717,28 +26835,28 @@
         <v>0.0369</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8578028877288034</v>
+        <v>0.8515340579106917</v>
       </c>
       <c r="J10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2594732439751076</v>
+        <v>0.2583576594282836</v>
       </c>
       <c r="M10" t="n">
-        <v>9.159525977126517</v>
+        <v>9.152699411633623</v>
       </c>
       <c r="N10" t="n">
-        <v>134.3969266585636</v>
+        <v>134.0115887142412</v>
       </c>
       <c r="O10" t="n">
-        <v>11.59296884575145</v>
+        <v>11.5763374481846</v>
       </c>
       <c r="P10" t="n">
-        <v>409.8939455829814</v>
+        <v>409.9506190182178</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26795,28 +26913,28 @@
         <v>0.0378</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8580133532502836</v>
+        <v>0.8573066784460978</v>
       </c>
       <c r="J11" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K11" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2353976730083598</v>
+        <v>0.2370136370750259</v>
       </c>
       <c r="M11" t="n">
-        <v>9.673157391536082</v>
+        <v>9.631561377143314</v>
       </c>
       <c r="N11" t="n">
-        <v>153.0339190279378</v>
+        <v>152.328438730749</v>
       </c>
       <c r="O11" t="n">
-        <v>12.37068789631109</v>
+        <v>12.34214076774159</v>
       </c>
       <c r="P11" t="n">
-        <v>408.6531886068926</v>
+        <v>408.6595773093953</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26873,28 +26991,28 @@
         <v>0.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7429157547333846</v>
+        <v>0.747331926928975</v>
       </c>
       <c r="J12" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1840284863000354</v>
+        <v>0.1873261842566804</v>
       </c>
       <c r="M12" t="n">
-        <v>9.841730821466856</v>
+        <v>9.818944178610705</v>
       </c>
       <c r="N12" t="n">
-        <v>153.4948078392496</v>
+        <v>152.8918870201436</v>
       </c>
       <c r="O12" t="n">
-        <v>12.38930215303709</v>
+        <v>12.36494589636945</v>
       </c>
       <c r="P12" t="n">
-        <v>408.9373466633339</v>
+        <v>408.8966259086841</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26951,28 +27069,28 @@
         <v>0.0375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6960577412410848</v>
+        <v>0.7025287855421822</v>
       </c>
       <c r="J13" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K13" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1597808905401069</v>
+        <v>0.1635181333074203</v>
       </c>
       <c r="M13" t="n">
-        <v>10.13934097836666</v>
+        <v>10.12198363286144</v>
       </c>
       <c r="N13" t="n">
-        <v>163.051353967225</v>
+        <v>162.5488846036913</v>
       </c>
       <c r="O13" t="n">
-        <v>12.7691563529947</v>
+        <v>12.74946605170943</v>
       </c>
       <c r="P13" t="n">
-        <v>405.6568433471447</v>
+        <v>405.598341789318</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27029,28 +27147,28 @@
         <v>0.0353</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7006804689207297</v>
+        <v>0.7077812840103188</v>
       </c>
       <c r="J14" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K14" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1663803724878542</v>
+        <v>0.1704208973429121</v>
       </c>
       <c r="M14" t="n">
-        <v>9.939577626750305</v>
+        <v>9.929572257082441</v>
       </c>
       <c r="N14" t="n">
-        <v>157.4243901844069</v>
+        <v>156.9994895862077</v>
       </c>
       <c r="O14" t="n">
-        <v>12.54688766923523</v>
+        <v>12.52994371839745</v>
       </c>
       <c r="P14" t="n">
-        <v>404.2241921331714</v>
+        <v>404.1599971245682</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27107,28 +27225,28 @@
         <v>0.0359</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6255775242804186</v>
+        <v>0.6341035609543119</v>
       </c>
       <c r="J15" t="n">
+        <v>216</v>
+      </c>
+      <c r="K15" t="n">
         <v>215</v>
       </c>
-      <c r="K15" t="n">
-        <v>214</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1383666918236016</v>
+        <v>0.1425844051565903</v>
       </c>
       <c r="M15" t="n">
-        <v>9.623204715283476</v>
+        <v>9.614314447697524</v>
       </c>
       <c r="N15" t="n">
-        <v>154.349049191198</v>
+        <v>154.0630500842646</v>
       </c>
       <c r="O15" t="n">
-        <v>12.423729278731</v>
+        <v>12.41221374631716</v>
       </c>
       <c r="P15" t="n">
-        <v>403.9988584497844</v>
+        <v>403.9209900918951</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27185,28 +27303,28 @@
         <v>0.0309</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3830946353768993</v>
+        <v>0.3930106514946195</v>
       </c>
       <c r="J16" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K16" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05757669304507762</v>
+        <v>0.06080454643518818</v>
       </c>
       <c r="M16" t="n">
-        <v>9.886416196543387</v>
+        <v>9.882607081924931</v>
       </c>
       <c r="N16" t="n">
-        <v>150.6732135260629</v>
+        <v>150.5456316852076</v>
       </c>
       <c r="O16" t="n">
-        <v>12.2749017725627</v>
+        <v>12.2697038140783</v>
       </c>
       <c r="P16" t="n">
-        <v>403.1420759722836</v>
+        <v>403.0506421147368</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27263,28 +27381,28 @@
         <v>0.0256</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06510116932272617</v>
+        <v>-0.05692369906181886</v>
       </c>
       <c r="J17" t="n">
+        <v>216</v>
+      </c>
+      <c r="K17" t="n">
         <v>215</v>
       </c>
-      <c r="K17" t="n">
-        <v>214</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.001694789511554773</v>
+        <v>0.00130689201275247</v>
       </c>
       <c r="M17" t="n">
-        <v>10.35073066837807</v>
+        <v>10.33974229085594</v>
       </c>
       <c r="N17" t="n">
-        <v>160.2285053273043</v>
+        <v>159.8852533980185</v>
       </c>
       <c r="O17" t="n">
-        <v>12.65813988417352</v>
+        <v>12.64457406945835</v>
       </c>
       <c r="P17" t="n">
-        <v>401.2224732582226</v>
+        <v>401.1487757098895</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27341,28 +27459,28 @@
         <v>0.0209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2249551685953967</v>
+        <v>0.2249332214605668</v>
       </c>
       <c r="J18" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K18" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01207456600025336</v>
+        <v>0.01220032580509967</v>
       </c>
       <c r="M18" t="n">
-        <v>13.31117174649847</v>
+        <v>13.24933241260817</v>
       </c>
       <c r="N18" t="n">
-        <v>264.9785658553893</v>
+        <v>263.7362292142939</v>
       </c>
       <c r="O18" t="n">
-        <v>16.27816223826846</v>
+        <v>16.23995779595175</v>
       </c>
       <c r="P18" t="n">
-        <v>385.2569653680021</v>
+        <v>385.2575064214759</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27419,28 +27537,28 @@
         <v>0.0255</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2093519005415048</v>
+        <v>0.2103124356872766</v>
       </c>
       <c r="J19" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K19" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01159867799764369</v>
+        <v>0.01182737058855132</v>
       </c>
       <c r="M19" t="n">
-        <v>12.05483129730322</v>
+        <v>12.00372481241764</v>
       </c>
       <c r="N19" t="n">
-        <v>239.0258097395373</v>
+        <v>237.9247699070178</v>
       </c>
       <c r="O19" t="n">
-        <v>15.46045955783777</v>
+        <v>15.42481020651528</v>
       </c>
       <c r="P19" t="n">
-        <v>388.5277012350189</v>
+        <v>388.5190175048882</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -27497,28 +27615,28 @@
         <v>0.0308</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5454360646703955</v>
+        <v>0.5474894948152895</v>
       </c>
       <c r="J20" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K20" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1185541289319038</v>
+        <v>0.120447777896041</v>
       </c>
       <c r="M20" t="n">
-        <v>9.365752421143133</v>
+        <v>9.331345895992051</v>
       </c>
       <c r="N20" t="n">
-        <v>139.2984606565507</v>
+        <v>138.6663139276561</v>
       </c>
       <c r="O20" t="n">
-        <v>11.80247688650779</v>
+        <v>11.77566617765874</v>
       </c>
       <c r="P20" t="n">
-        <v>382.645970607397</v>
+        <v>382.62701442081</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -27575,28 +27693,28 @@
         <v>0.0381</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5298333104213867</v>
+        <v>0.5350996425472972</v>
       </c>
       <c r="J21" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K21" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1340099026654678</v>
+        <v>0.1374027528339271</v>
       </c>
       <c r="M21" t="n">
-        <v>8.248265495474467</v>
+        <v>8.233524289675533</v>
       </c>
       <c r="N21" t="n">
-        <v>115.0602415033437</v>
+        <v>114.6731506850192</v>
       </c>
       <c r="O21" t="n">
-        <v>10.72661370159958</v>
+        <v>10.70855502320548</v>
       </c>
       <c r="P21" t="n">
-        <v>382.2145995747593</v>
+        <v>382.1658681322331</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -27653,28 +27771,28 @@
         <v>0.0421</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3848358894247537</v>
+        <v>0.3875578943944649</v>
       </c>
       <c r="J22" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K22" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0795555284625904</v>
+        <v>0.08134519829034237</v>
       </c>
       <c r="M22" t="n">
-        <v>8.071205289871989</v>
+        <v>8.047501607701712</v>
       </c>
       <c r="N22" t="n">
-        <v>110.7014095068369</v>
+        <v>110.2198284904282</v>
       </c>
       <c r="O22" t="n">
-        <v>10.52147373264967</v>
+        <v>10.49856316313943</v>
       </c>
       <c r="P22" t="n">
-        <v>383.4131117100288</v>
+        <v>383.3883691127973</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -27731,28 +27849,28 @@
         <v>0.0526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3314102146428237</v>
+        <v>0.3280484993493441</v>
       </c>
       <c r="J23" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K23" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05791518639855542</v>
+        <v>0.05735685511473299</v>
       </c>
       <c r="M23" t="n">
-        <v>8.068669097025346</v>
+        <v>8.048147849323286</v>
       </c>
       <c r="N23" t="n">
-        <v>112.0608555503766</v>
+        <v>111.6034658130039</v>
       </c>
       <c r="O23" t="n">
-        <v>10.58588000831186</v>
+        <v>10.56425415318109</v>
       </c>
       <c r="P23" t="n">
-        <v>381.5084999842014</v>
+        <v>381.5394977754117</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -27809,28 +27927,28 @@
         <v>0.0468</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5758130910803548</v>
+        <v>0.5652883120902371</v>
       </c>
       <c r="J24" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K24" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1743738136773573</v>
+        <v>0.1697028131142787</v>
       </c>
       <c r="M24" t="n">
-        <v>8.030511586535312</v>
+        <v>8.042073347209607</v>
       </c>
       <c r="N24" t="n">
-        <v>98.4668105580657</v>
+        <v>98.65614133847981</v>
       </c>
       <c r="O24" t="n">
-        <v>9.923044419837376</v>
+        <v>9.932579792706415</v>
       </c>
       <c r="P24" t="n">
-        <v>376.8924888028884</v>
+        <v>376.9895359568532</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -27887,28 +28005,28 @@
         <v>0.0457</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4855765898691817</v>
+        <v>0.4728094597323494</v>
       </c>
       <c r="J25" t="n">
+        <v>216</v>
+      </c>
+      <c r="K25" t="n">
         <v>215</v>
       </c>
-      <c r="K25" t="n">
-        <v>214</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1330407320911735</v>
+        <v>0.1270888149888102</v>
       </c>
       <c r="M25" t="n">
-        <v>8.2781024305977</v>
+        <v>8.301695139086226</v>
       </c>
       <c r="N25" t="n">
-        <v>97.63021468632138</v>
+        <v>98.14961694555971</v>
       </c>
       <c r="O25" t="n">
-        <v>9.880800305963145</v>
+        <v>9.907048851477402</v>
       </c>
       <c r="P25" t="n">
-        <v>376.365749525563</v>
+        <v>376.4820806047257</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -27965,28 +28083,28 @@
         <v>0.0465</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3327541474479139</v>
+        <v>0.3230325749282332</v>
       </c>
       <c r="J26" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K26" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06828101587307212</v>
+        <v>0.06488980222590091</v>
       </c>
       <c r="M26" t="n">
-        <v>8.235249571367349</v>
+        <v>8.242515323883502</v>
       </c>
       <c r="N26" t="n">
-        <v>96.37298855656776</v>
+        <v>96.49026311171042</v>
       </c>
       <c r="O26" t="n">
-        <v>9.816974511353678</v>
+        <v>9.822945745127091</v>
       </c>
       <c r="P26" t="n">
-        <v>377.3161085809655</v>
+        <v>377.4045793240288</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -28043,28 +28161,28 @@
         <v>0.0476</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0444361254953959</v>
+        <v>0.04186443988019179</v>
       </c>
       <c r="J27" t="n">
+        <v>216</v>
+      </c>
+      <c r="K27" t="n">
         <v>215</v>
       </c>
-      <c r="K27" t="n">
-        <v>214</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.001188622357656377</v>
+        <v>0.001066044942090727</v>
       </c>
       <c r="M27" t="n">
-        <v>8.592256290706818</v>
+        <v>8.562892612872844</v>
       </c>
       <c r="N27" t="n">
-        <v>105.4305932438021</v>
+        <v>104.9797171529356</v>
       </c>
       <c r="O27" t="n">
-        <v>10.2679400681832</v>
+        <v>10.24596101656334</v>
       </c>
       <c r="P27" t="n">
-        <v>379.7993885914494</v>
+        <v>379.8228211843405</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -28121,28 +28239,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.04607573047296828</v>
+        <v>-0.04394164098550754</v>
       </c>
       <c r="J28" t="n">
+        <v>216</v>
+      </c>
+      <c r="K28" t="n">
         <v>215</v>
       </c>
-      <c r="K28" t="n">
-        <v>214</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.001130349024805688</v>
+        <v>0.001038925499109999</v>
       </c>
       <c r="M28" t="n">
-        <v>8.911543556014141</v>
+        <v>8.881307325189479</v>
       </c>
       <c r="N28" t="n">
-        <v>119.2052567386924</v>
+        <v>118.6780139393283</v>
       </c>
       <c r="O28" t="n">
-        <v>10.91811598851617</v>
+        <v>10.89394391115212</v>
       </c>
       <c r="P28" t="n">
-        <v>376.4093858561426</v>
+        <v>376.389940535977</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -28199,28 +28317,28 @@
         <v>0.045</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.06311341171586292</v>
+        <v>-0.0543563998161762</v>
       </c>
       <c r="J29" t="n">
+        <v>216</v>
+      </c>
+      <c r="K29" t="n">
         <v>215</v>
       </c>
-      <c r="K29" t="n">
-        <v>214</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.001648247047674523</v>
+        <v>0.001232489413921178</v>
       </c>
       <c r="M29" t="n">
-        <v>10.15323178093681</v>
+        <v>10.14853476390885</v>
       </c>
       <c r="N29" t="n">
-        <v>153.3060479854085</v>
+        <v>153.0509904069966</v>
       </c>
       <c r="O29" t="n">
-        <v>12.38168195300657</v>
+        <v>12.37137787018878</v>
       </c>
       <c r="P29" t="n">
-        <v>370.0790814154801</v>
+        <v>369.9992895880599</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -28277,28 +28395,28 @@
         <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.09648748241742588</v>
+        <v>-0.08532588843782796</v>
       </c>
       <c r="J30" t="n">
+        <v>216</v>
+      </c>
+      <c r="K30" t="n">
         <v>215</v>
       </c>
-      <c r="K30" t="n">
-        <v>214</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.002641872206361251</v>
+        <v>0.002082319524838394</v>
       </c>
       <c r="M30" t="n">
-        <v>12.47871922002312</v>
+        <v>12.48618879557594</v>
       </c>
       <c r="N30" t="n">
-        <v>223.3242941515331</v>
+        <v>223.029623156584</v>
       </c>
       <c r="O30" t="n">
-        <v>14.94403874966648</v>
+        <v>14.93417634677534</v>
       </c>
       <c r="P30" t="n">
-        <v>360.2035314938876</v>
+        <v>360.1018296815849</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -28355,28 +28473,28 @@
         <v>0.0481</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3048065118470649</v>
+        <v>-0.2940881485739334</v>
       </c>
       <c r="J31" t="n">
+        <v>216</v>
+      </c>
+      <c r="K31" t="n">
         <v>215</v>
       </c>
-      <c r="K31" t="n">
-        <v>214</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.03246490846626582</v>
+        <v>0.0304882420339303</v>
       </c>
       <c r="M31" t="n">
-        <v>10.88708211919259</v>
+        <v>10.88984903654973</v>
       </c>
       <c r="N31" t="n">
-        <v>175.936407506807</v>
+        <v>175.8042258894335</v>
       </c>
       <c r="O31" t="n">
-        <v>13.2641022126191</v>
+        <v>13.25911859398782</v>
       </c>
       <c r="P31" t="n">
-        <v>352.6029003462123</v>
+        <v>352.5052371475876</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -28433,28 +28551,28 @@
         <v>0.0455</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3731384840939117</v>
+        <v>-0.3675467687378557</v>
       </c>
       <c r="J32" t="n">
+        <v>216</v>
+      </c>
+      <c r="K32" t="n">
         <v>215</v>
       </c>
-      <c r="K32" t="n">
-        <v>214</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.08798800456442579</v>
+        <v>0.08627037509019864</v>
       </c>
       <c r="M32" t="n">
-        <v>7.860559337561882</v>
+        <v>7.85174644649192</v>
       </c>
       <c r="N32" t="n">
-        <v>91.70053356760305</v>
+        <v>91.46075966579505</v>
       </c>
       <c r="O32" t="n">
-        <v>9.576039555453134</v>
+        <v>9.563511889771197</v>
       </c>
       <c r="P32" t="n">
-        <v>351.8019837450141</v>
+        <v>351.7510333532841</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -28511,28 +28629,28 @@
         <v>0.0372</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8070737256836585</v>
+        <v>-0.8018620393619688</v>
       </c>
       <c r="J33" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K33" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2236029847116464</v>
+        <v>0.223000225156297</v>
       </c>
       <c r="M33" t="n">
-        <v>9.487914011485854</v>
+        <v>9.462549574770351</v>
       </c>
       <c r="N33" t="n">
-        <v>147.1215650568712</v>
+        <v>146.5874767937689</v>
       </c>
       <c r="O33" t="n">
-        <v>12.12936787540353</v>
+        <v>12.10733153067879</v>
       </c>
       <c r="P33" t="n">
-        <v>349.0268275953337</v>
+        <v>348.9799423086013</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -28570,7 +28688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH216"/>
+  <dimension ref="A1:AH217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65377,7 +65495,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>-35.282111547747384,173.15090027070093</t>
+          <t>-35.28213759787128,173.15086175876746</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -65458,6 +65576,178 @@
       <c r="AH216" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>-35.291408399170116,173.1596650465579</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>-35.29090478680739,173.15899852178703</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>-35.290364381775035,173.15838821127142</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-35.289810866039865,173.157797928205</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-35.28923130227429,173.15724744150856</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-35.288618715836236,173.1567474087644</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-35.28802333806174,173.15622107418736</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-35.28744769996326,173.1556645703225</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-35.28689090129034,173.15507927276482</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-35.28634669814856,173.15447472238986</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-35.285790565974295,173.15388839388527</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-35.28520568669232,173.15334598618676</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-35.284629863049396,173.1527914218251</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>-35.284057984597666,173.1522387173391</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>-35.28346213282213,173.15171944424796</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>-35.28280683855901,173.15128029554805</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>-35.28211395767126,173.150896707924</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>-35.28159665317643,173.1502535457608</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>-35.28105507313218,173.1496462661161</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>-35.28050516905881,173.1490512866749</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>-35.27990809614331,173.14852603511065</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>-35.27928359292364,173.14804133018717</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>-35.27868203727379,173.147522694084</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>-35.278083977988985,173.14699888316744</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>-35.277520341329755,173.1464241766994</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>-35.276974148565,173.14582911870033</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>-35.27642935147399,173.14523573835947</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>-35.27589871249922,173.14461783274277</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>-35.275313064834734,173.14406962704751</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>-35.27469291088026,173.14356653005171</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>-35.27410442787062,173.14302202206505</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>-35.273477748663126,173.1425274468009</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0067/nzd0067.xlsx
+++ b/data/nzd0067/nzd0067.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH217"/>
+  <dimension ref="A1:AH219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23796,6 +23796,222 @@
       <c r="AH217" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>419.04</v>
+      </c>
+      <c r="C218" t="n">
+        <v>433.03</v>
+      </c>
+      <c r="D218" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="E218" t="n">
+        <v>440.03</v>
+      </c>
+      <c r="F218" t="n">
+        <v>437.65</v>
+      </c>
+      <c r="G218" t="n">
+        <v>425.61</v>
+      </c>
+      <c r="H218" t="n">
+        <v>420.28</v>
+      </c>
+      <c r="I218" t="n">
+        <v>420.43</v>
+      </c>
+      <c r="J218" t="n">
+        <v>425.95</v>
+      </c>
+      <c r="K218" t="n">
+        <v>432.45</v>
+      </c>
+      <c r="L218" t="n">
+        <v>435.01</v>
+      </c>
+      <c r="M218" t="n">
+        <v>434.41</v>
+      </c>
+      <c r="N218" t="n">
+        <v>433.82</v>
+      </c>
+      <c r="O218" t="n">
+        <v>433.3</v>
+      </c>
+      <c r="P218" t="n">
+        <v>427.02</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>415.17</v>
+      </c>
+      <c r="R218" t="n">
+        <v>394.15</v>
+      </c>
+      <c r="S218" t="n">
+        <v>403.72</v>
+      </c>
+      <c r="T218" t="n">
+        <v>405.12</v>
+      </c>
+      <c r="U218" t="n">
+        <v>407.86</v>
+      </c>
+      <c r="V218" t="n">
+        <v>402.23</v>
+      </c>
+      <c r="W218" t="n">
+        <v>392.62</v>
+      </c>
+      <c r="X218" t="n">
+        <v>386.61</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>378</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>379.37</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>382.04</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>375.86</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>362.63</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>340.56</v>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>425.05</v>
+      </c>
+      <c r="C219" t="n">
+        <v>438.43</v>
+      </c>
+      <c r="D219" t="n">
+        <v>442.38</v>
+      </c>
+      <c r="E219" t="n">
+        <v>441.95</v>
+      </c>
+      <c r="F219" t="n">
+        <v>439.59</v>
+      </c>
+      <c r="G219" t="n">
+        <v>428.77</v>
+      </c>
+      <c r="H219" t="n">
+        <v>425.32</v>
+      </c>
+      <c r="I219" t="n">
+        <v>425.54</v>
+      </c>
+      <c r="J219" t="n">
+        <v>429.87</v>
+      </c>
+      <c r="K219" t="n">
+        <v>435.32</v>
+      </c>
+      <c r="L219" t="n">
+        <v>437.34</v>
+      </c>
+      <c r="M219" t="n">
+        <v>434.02</v>
+      </c>
+      <c r="N219" t="n">
+        <v>432.23</v>
+      </c>
+      <c r="O219" t="n">
+        <v>430.89</v>
+      </c>
+      <c r="P219" t="n">
+        <v>424.24</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>416.08</v>
+      </c>
+      <c r="R219" t="n">
+        <v>395.95</v>
+      </c>
+      <c r="S219" t="n">
+        <v>410.44</v>
+      </c>
+      <c r="T219" t="n">
+        <v>406.92</v>
+      </c>
+      <c r="U219" t="n">
+        <v>412.13</v>
+      </c>
+      <c r="V219" t="n">
+        <v>407.21</v>
+      </c>
+      <c r="W219" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="X219" t="n">
+        <v>393.47</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>389.79</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>379.61</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>378.39</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>371.16</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>357.08</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>341.46</v>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23810,7 +24026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B223"/>
+  <dimension ref="A1:B225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26043,6 +26259,26 @@
       </c>
       <c r="B223" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -26211,28 +26447,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.163069054370548</v>
+        <v>0.1719819903770749</v>
       </c>
       <c r="J2" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K2" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01321797348149134</v>
+        <v>0.01495160319602007</v>
       </c>
       <c r="M2" t="n">
-        <v>8.911485696189347</v>
+        <v>8.876494466437959</v>
       </c>
       <c r="N2" t="n">
-        <v>126.6201595590426</v>
+        <v>125.7655928551846</v>
       </c>
       <c r="O2" t="n">
-        <v>11.25256235526125</v>
+        <v>11.21452597550091</v>
       </c>
       <c r="P2" t="n">
-        <v>412.5605188407648</v>
+        <v>412.4783210759288</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26289,28 +26525,28 @@
         <v>0.0361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1572451650059616</v>
+        <v>0.173732128984762</v>
       </c>
       <c r="J3" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01329490780027287</v>
+        <v>0.01639744714140223</v>
       </c>
       <c r="M3" t="n">
-        <v>8.139690172660861</v>
+        <v>8.1469699306367</v>
       </c>
       <c r="N3" t="n">
-        <v>116.4526651949139</v>
+        <v>116.2441885810187</v>
       </c>
       <c r="O3" t="n">
-        <v>10.79132360718156</v>
+        <v>10.78165982495361</v>
       </c>
       <c r="P3" t="n">
-        <v>422.0803648451133</v>
+        <v>421.9270558846605</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26367,28 +26603,28 @@
         <v>0.0434</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2648244977526142</v>
+        <v>0.2777150816962454</v>
       </c>
       <c r="J4" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K4" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02608751436050516</v>
+        <v>0.02911763307691551</v>
       </c>
       <c r="M4" t="n">
-        <v>9.723055944008268</v>
+        <v>9.695641448907153</v>
       </c>
       <c r="N4" t="n">
-        <v>163.7396742226505</v>
+        <v>162.7135692420555</v>
       </c>
       <c r="O4" t="n">
-        <v>12.79608042420219</v>
+        <v>12.75592290828286</v>
       </c>
       <c r="P4" t="n">
-        <v>426.0937580061784</v>
+        <v>425.9719999976887</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26445,28 +26681,28 @@
         <v>0.0469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3247891278309323</v>
+        <v>0.3327407834943192</v>
       </c>
       <c r="J5" t="n">
+        <v>218</v>
+      </c>
+      <c r="K5" t="n">
         <v>216</v>
       </c>
-      <c r="K5" t="n">
-        <v>214</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.03969646142521588</v>
+        <v>0.04238190198947778</v>
       </c>
       <c r="M5" t="n">
-        <v>9.858786235378043</v>
+        <v>9.803238766959257</v>
       </c>
       <c r="N5" t="n">
-        <v>162.8857573007628</v>
+        <v>161.5771421580965</v>
       </c>
       <c r="O5" t="n">
-        <v>12.76267046118338</v>
+        <v>12.71129978240213</v>
       </c>
       <c r="P5" t="n">
-        <v>427.7362364813599</v>
+        <v>427.6630835800988</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26523,28 +26759,28 @@
         <v>0.045</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4607060116119787</v>
+        <v>0.464382357494394</v>
       </c>
       <c r="J6" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K6" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07454089111987738</v>
+        <v>0.07711403064929045</v>
       </c>
       <c r="M6" t="n">
-        <v>9.799382243479888</v>
+        <v>9.727485898466117</v>
       </c>
       <c r="N6" t="n">
-        <v>166.015890060852</v>
+        <v>164.5060287820484</v>
       </c>
       <c r="O6" t="n">
-        <v>12.88471536592299</v>
+        <v>12.82599036262106</v>
       </c>
       <c r="P6" t="n">
-        <v>424.2645694521679</v>
+        <v>424.230149501134</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26601,28 +26837,28 @@
         <v>0.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5736864921727483</v>
+        <v>0.5608606817871024</v>
       </c>
       <c r="J7" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K7" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1296824433707875</v>
+        <v>0.1265692668725208</v>
       </c>
       <c r="M7" t="n">
-        <v>9.577011102421171</v>
+        <v>9.561817366690526</v>
       </c>
       <c r="N7" t="n">
-        <v>142.2037157390247</v>
+        <v>141.4251444995925</v>
       </c>
       <c r="O7" t="n">
-        <v>11.92491994686022</v>
+        <v>11.89223042576928</v>
       </c>
       <c r="P7" t="n">
-        <v>419.4536270694122</v>
+        <v>419.5702867877492</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26679,28 +26915,28 @@
         <v>0.0427</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6497461088009191</v>
+        <v>0.6306563774834513</v>
       </c>
       <c r="J8" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K8" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1685000496010589</v>
+        <v>0.1619623834550814</v>
       </c>
       <c r="M8" t="n">
-        <v>9.249530513842204</v>
+        <v>9.252865203542918</v>
       </c>
       <c r="N8" t="n">
-        <v>134.6397539623289</v>
+        <v>134.5783704181128</v>
       </c>
       <c r="O8" t="n">
-        <v>11.60343716156247</v>
+        <v>11.60079180134325</v>
       </c>
       <c r="P8" t="n">
-        <v>416.7216943563801</v>
+        <v>416.8951108106803</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26757,28 +26993,28 @@
         <v>0.0432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7104876767756991</v>
+        <v>0.6932838444884019</v>
       </c>
       <c r="J9" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K9" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1909859112047467</v>
+        <v>0.1856367031599052</v>
       </c>
       <c r="M9" t="n">
-        <v>9.164462020237258</v>
+        <v>9.169076777792778</v>
       </c>
       <c r="N9" t="n">
-        <v>137.6679955217183</v>
+        <v>137.370329604363</v>
       </c>
       <c r="O9" t="n">
-        <v>11.73320056598873</v>
+        <v>11.7205089311157</v>
       </c>
       <c r="P9" t="n">
-        <v>414.18006208832</v>
+        <v>414.3365356891332</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26835,28 +27071,28 @@
         <v>0.0369</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8515340579106917</v>
+        <v>0.8435528297662986</v>
       </c>
       <c r="J10" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K10" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2583576594282836</v>
+        <v>0.2584565130362541</v>
       </c>
       <c r="M10" t="n">
-        <v>9.152699411633623</v>
+        <v>9.113835742290359</v>
       </c>
       <c r="N10" t="n">
-        <v>134.0115887142412</v>
+        <v>133.011794484077</v>
       </c>
       <c r="O10" t="n">
-        <v>11.5763374481846</v>
+        <v>11.53307393907093</v>
       </c>
       <c r="P10" t="n">
-        <v>409.9506190182178</v>
+        <v>410.0231978629063</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26913,28 +27149,28 @@
         <v>0.0378</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8573066784460978</v>
+        <v>0.8614543679014287</v>
       </c>
       <c r="J11" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K11" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2370136370750259</v>
+        <v>0.2425293878461092</v>
       </c>
       <c r="M11" t="n">
-        <v>9.631561377143314</v>
+        <v>9.568151828044801</v>
       </c>
       <c r="N11" t="n">
-        <v>152.328438730749</v>
+        <v>151.0018984728716</v>
       </c>
       <c r="O11" t="n">
-        <v>12.34214076774159</v>
+        <v>12.28828297496731</v>
       </c>
       <c r="P11" t="n">
-        <v>408.6595773093953</v>
+        <v>408.6218192315554</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26991,28 +27227,28 @@
         <v>0.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.747331926928975</v>
+        <v>0.7602042033883188</v>
       </c>
       <c r="J12" t="n">
+        <v>218</v>
+      </c>
+      <c r="K12" t="n">
         <v>216</v>
       </c>
-      <c r="K12" t="n">
-        <v>214</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1873261842566804</v>
+        <v>0.1953816422173241</v>
       </c>
       <c r="M12" t="n">
-        <v>9.818944178610705</v>
+        <v>9.794346256318009</v>
       </c>
       <c r="N12" t="n">
-        <v>152.8918870201436</v>
+        <v>151.9810533446696</v>
       </c>
       <c r="O12" t="n">
-        <v>12.36494589636945</v>
+        <v>12.3280595936534</v>
       </c>
       <c r="P12" t="n">
-        <v>408.8966259086841</v>
+        <v>408.7771757496496</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27069,28 +27305,28 @@
         <v>0.0375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7025287855421822</v>
+        <v>0.7194830357623631</v>
       </c>
       <c r="J13" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K13" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1635181333074203</v>
+        <v>0.172365201802653</v>
       </c>
       <c r="M13" t="n">
-        <v>10.12198363286144</v>
+        <v>10.10516630522951</v>
       </c>
       <c r="N13" t="n">
-        <v>162.5488846036913</v>
+        <v>161.9372285908932</v>
       </c>
       <c r="O13" t="n">
-        <v>12.74946605170943</v>
+        <v>12.72545592860599</v>
       </c>
       <c r="P13" t="n">
-        <v>405.598341789318</v>
+        <v>405.4441001301302</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27147,28 +27383,28 @@
         <v>0.0353</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7077812840103188</v>
+        <v>0.7249176483949126</v>
       </c>
       <c r="J14" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K14" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1704208973429121</v>
+        <v>0.1795320747463166</v>
       </c>
       <c r="M14" t="n">
-        <v>9.929572257082441</v>
+        <v>9.927399018505822</v>
       </c>
       <c r="N14" t="n">
-        <v>156.9994895862077</v>
+        <v>156.463607430437</v>
       </c>
       <c r="O14" t="n">
-        <v>12.52994371839745</v>
+        <v>12.50854137901126</v>
       </c>
       <c r="P14" t="n">
-        <v>404.1599971245682</v>
+        <v>404.0041086638468</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27225,28 +27461,28 @@
         <v>0.0359</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6341035609543119</v>
+        <v>0.6535815161561815</v>
       </c>
       <c r="J15" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K15" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1425844051565903</v>
+        <v>0.1518873262492558</v>
       </c>
       <c r="M15" t="n">
-        <v>9.614314447697524</v>
+        <v>9.605801657863708</v>
       </c>
       <c r="N15" t="n">
-        <v>154.0630500842646</v>
+        <v>153.8011250522904</v>
       </c>
       <c r="O15" t="n">
-        <v>12.41221374631716</v>
+        <v>12.40165815737115</v>
       </c>
       <c r="P15" t="n">
-        <v>403.9209900918951</v>
+        <v>403.7420031020241</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27303,28 +27539,28 @@
         <v>0.0309</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3930106514946195</v>
+        <v>0.414079543896363</v>
       </c>
       <c r="J16" t="n">
+        <v>218</v>
+      </c>
+      <c r="K16" t="n">
         <v>216</v>
       </c>
-      <c r="K16" t="n">
-        <v>214</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.06080454643518818</v>
+        <v>0.06782311294932331</v>
       </c>
       <c r="M16" t="n">
-        <v>9.882607081924931</v>
+        <v>9.879271587736381</v>
       </c>
       <c r="N16" t="n">
-        <v>150.5456316852076</v>
+        <v>150.4911287194539</v>
       </c>
       <c r="O16" t="n">
-        <v>12.2697038140783</v>
+        <v>12.26748257465459</v>
       </c>
       <c r="P16" t="n">
-        <v>403.0506421147368</v>
+        <v>402.8551857226857</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27381,28 +27617,28 @@
         <v>0.0256</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.05692369906181886</v>
+        <v>-0.02955476277067781</v>
       </c>
       <c r="J17" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K17" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00130689201275247</v>
+        <v>0.0003550584681184521</v>
       </c>
       <c r="M17" t="n">
-        <v>10.33974229085594</v>
+        <v>10.36850918334892</v>
       </c>
       <c r="N17" t="n">
-        <v>159.8852533980185</v>
+        <v>160.6987560437591</v>
       </c>
       <c r="O17" t="n">
-        <v>12.64457406945835</v>
+        <v>12.67670130766514</v>
       </c>
       <c r="P17" t="n">
-        <v>401.1487757098895</v>
+        <v>400.9005473851897</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27459,28 +27695,28 @@
         <v>0.0209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2249332214605668</v>
+        <v>0.2314342528370372</v>
       </c>
       <c r="J18" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K18" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01220032580509967</v>
+        <v>0.0131710301942376</v>
       </c>
       <c r="M18" t="n">
-        <v>13.24933241260817</v>
+        <v>13.15622480712823</v>
       </c>
       <c r="N18" t="n">
-        <v>263.7362292142939</v>
+        <v>261.453134188811</v>
       </c>
       <c r="O18" t="n">
-        <v>16.23995779595175</v>
+        <v>16.16951249075899</v>
       </c>
       <c r="P18" t="n">
-        <v>385.2575064214759</v>
+        <v>385.1983469637253</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27537,28 +27773,28 @@
         <v>0.0255</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2103124356872766</v>
+        <v>0.2324477814029485</v>
       </c>
       <c r="J19" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K19" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01182737058855132</v>
+        <v>0.01461495883262465</v>
       </c>
       <c r="M19" t="n">
-        <v>12.00372481241764</v>
+        <v>12.00171635998926</v>
       </c>
       <c r="N19" t="n">
-        <v>237.9247699070178</v>
+        <v>237.34255587755</v>
       </c>
       <c r="O19" t="n">
-        <v>15.42481020651528</v>
+        <v>15.4059259987042</v>
       </c>
       <c r="P19" t="n">
-        <v>388.5190175048882</v>
+        <v>388.3175804807113</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -27615,28 +27851,28 @@
         <v>0.0308</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5474894948152895</v>
+        <v>0.5628553147656732</v>
       </c>
       <c r="J20" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K20" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L20" t="n">
-        <v>0.120447777896041</v>
+        <v>0.1282100819821785</v>
       </c>
       <c r="M20" t="n">
-        <v>9.331345895992051</v>
+        <v>9.316625982011983</v>
       </c>
       <c r="N20" t="n">
-        <v>138.6663139276561</v>
+        <v>138.0854521027489</v>
       </c>
       <c r="O20" t="n">
-        <v>11.77566617765874</v>
+        <v>11.75097664463465</v>
       </c>
       <c r="P20" t="n">
-        <v>382.62701442081</v>
+        <v>382.4842574586332</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -27693,28 +27929,28 @@
         <v>0.0381</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5350996425472972</v>
+        <v>0.5588234932469283</v>
       </c>
       <c r="J21" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K21" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1374027528339271</v>
+        <v>0.1487358972711734</v>
       </c>
       <c r="M21" t="n">
-        <v>8.233524289675533</v>
+        <v>8.265036243731982</v>
       </c>
       <c r="N21" t="n">
-        <v>114.6731506850192</v>
+        <v>115.33255846829</v>
       </c>
       <c r="O21" t="n">
-        <v>10.70855502320548</v>
+        <v>10.73929971964141</v>
       </c>
       <c r="P21" t="n">
-        <v>382.1658681322331</v>
+        <v>381.9448913153664</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -27771,28 +28007,28 @@
         <v>0.0421</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3875578943944649</v>
+        <v>0.4064622352766584</v>
       </c>
       <c r="J22" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K22" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08134519829034237</v>
+        <v>0.08957943871625451</v>
       </c>
       <c r="M22" t="n">
-        <v>8.047501607701712</v>
+        <v>8.071874574903916</v>
       </c>
       <c r="N22" t="n">
-        <v>110.2198284904282</v>
+        <v>110.3518434681267</v>
       </c>
       <c r="O22" t="n">
-        <v>10.49856316313943</v>
+        <v>10.50484856950002</v>
       </c>
       <c r="P22" t="n">
-        <v>383.3883691127973</v>
+        <v>383.2153640903748</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -27849,28 +28085,28 @@
         <v>0.0526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3280484993493441</v>
+        <v>0.3366760498048135</v>
       </c>
       <c r="J23" t="n">
+        <v>218</v>
+      </c>
+      <c r="K23" t="n">
         <v>216</v>
       </c>
-      <c r="K23" t="n">
-        <v>214</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.05735685511473299</v>
+        <v>0.06129527110708799</v>
       </c>
       <c r="M23" t="n">
-        <v>8.048147849323286</v>
+        <v>8.019602121671822</v>
       </c>
       <c r="N23" t="n">
-        <v>111.6034658130039</v>
+        <v>110.8534508003985</v>
       </c>
       <c r="O23" t="n">
-        <v>10.56425415318109</v>
+        <v>10.52869653852738</v>
       </c>
       <c r="P23" t="n">
-        <v>381.5394977754117</v>
+        <v>381.459406248383</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -27927,28 +28163,28 @@
         <v>0.0468</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5652883120902371</v>
+        <v>0.5618624825589172</v>
       </c>
       <c r="J24" t="n">
+        <v>218</v>
+      </c>
+      <c r="K24" t="n">
         <v>216</v>
       </c>
-      <c r="K24" t="n">
-        <v>214</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.1697028131142787</v>
+        <v>0.1707783568667712</v>
       </c>
       <c r="M24" t="n">
-        <v>8.042073347209607</v>
+        <v>7.997188695609808</v>
       </c>
       <c r="N24" t="n">
-        <v>98.65614133847981</v>
+        <v>97.88600436145883</v>
       </c>
       <c r="O24" t="n">
-        <v>9.932579792706415</v>
+        <v>9.89373561206579</v>
       </c>
       <c r="P24" t="n">
-        <v>376.9895359568532</v>
+        <v>377.021263423427</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28005,28 +28241,28 @@
         <v>0.0457</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4728094597323494</v>
+        <v>0.4672410719831824</v>
       </c>
       <c r="J25" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K25" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1270888149888102</v>
+        <v>0.1265306207142713</v>
       </c>
       <c r="M25" t="n">
-        <v>8.301695139086226</v>
+        <v>8.259621568100979</v>
       </c>
       <c r="N25" t="n">
-        <v>98.14961694555971</v>
+        <v>97.48525145002463</v>
       </c>
       <c r="O25" t="n">
-        <v>9.907048851477402</v>
+        <v>9.873461978962832</v>
       </c>
       <c r="P25" t="n">
-        <v>376.4820806047257</v>
+        <v>376.5330712496574</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -28083,28 +28319,28 @@
         <v>0.0465</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3230325749282332</v>
+        <v>0.3164596388664913</v>
       </c>
       <c r="J26" t="n">
+        <v>218</v>
+      </c>
+      <c r="K26" t="n">
         <v>216</v>
       </c>
-      <c r="K26" t="n">
-        <v>214</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.06488980222590091</v>
+        <v>0.06350345275215241</v>
       </c>
       <c r="M26" t="n">
-        <v>8.242515323883502</v>
+        <v>8.200534311670159</v>
       </c>
       <c r="N26" t="n">
-        <v>96.49026311171042</v>
+        <v>95.8884033880658</v>
       </c>
       <c r="O26" t="n">
-        <v>9.822945745127091</v>
+        <v>9.792262424387216</v>
       </c>
       <c r="P26" t="n">
-        <v>377.4045793240288</v>
+        <v>377.4647056342101</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -28161,28 +28397,28 @@
         <v>0.0476</v>
       </c>
       <c r="I27" t="n">
-        <v>0.04186443988019179</v>
+        <v>0.04245782135440915</v>
       </c>
       <c r="J27" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K27" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001066044942090727</v>
+        <v>0.001119453277388605</v>
       </c>
       <c r="M27" t="n">
-        <v>8.562892612872844</v>
+        <v>8.502205076679958</v>
       </c>
       <c r="N27" t="n">
-        <v>104.9797171529356</v>
+        <v>104.0465874280573</v>
       </c>
       <c r="O27" t="n">
-        <v>10.24596101656334</v>
+        <v>10.20032290802881</v>
       </c>
       <c r="P27" t="n">
-        <v>379.8228211843405</v>
+        <v>379.8173485255861</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -28239,28 +28475,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.04394164098550754</v>
+        <v>-0.03652037048504778</v>
       </c>
       <c r="J28" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K28" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L28" t="n">
-        <v>0.001038925499109999</v>
+        <v>0.0007321363856437335</v>
       </c>
       <c r="M28" t="n">
-        <v>8.881307325189479</v>
+        <v>8.838381383242435</v>
       </c>
       <c r="N28" t="n">
-        <v>118.6780139393283</v>
+        <v>117.7511414579288</v>
       </c>
       <c r="O28" t="n">
-        <v>10.89394391115212</v>
+        <v>10.85131980258295</v>
       </c>
       <c r="P28" t="n">
-        <v>376.389940535977</v>
+        <v>376.3218928375805</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -28317,28 +28553,28 @@
         <v>0.045</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0543563998161762</v>
+        <v>-0.03432559669001194</v>
       </c>
       <c r="J29" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K29" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L29" t="n">
-        <v>0.001232489413921178</v>
+        <v>0.0004982555721367854</v>
       </c>
       <c r="M29" t="n">
-        <v>10.14853476390885</v>
+        <v>10.15029795528349</v>
       </c>
       <c r="N29" t="n">
-        <v>153.0509904069966</v>
+        <v>152.8876586024249</v>
       </c>
       <c r="O29" t="n">
-        <v>12.37137787018878</v>
+        <v>12.36477491111039</v>
       </c>
       <c r="P29" t="n">
-        <v>369.9992895880599</v>
+        <v>369.8156551365873</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -28395,28 +28631,28 @@
         <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.08532588843782796</v>
+        <v>-0.05840559343666834</v>
       </c>
       <c r="J30" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K30" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L30" t="n">
-        <v>0.002082319524838394</v>
+        <v>0.0009875236030043588</v>
       </c>
       <c r="M30" t="n">
-        <v>12.48618879557594</v>
+        <v>12.52615623050217</v>
       </c>
       <c r="N30" t="n">
-        <v>223.029623156584</v>
+        <v>223.2220828358344</v>
       </c>
       <c r="O30" t="n">
-        <v>14.93417634677534</v>
+        <v>14.94061855599809</v>
       </c>
       <c r="P30" t="n">
-        <v>360.1018296815849</v>
+        <v>359.8550333122656</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -28473,28 +28709,28 @@
         <v>0.0481</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2940881485739334</v>
+        <v>-0.2655679816668012</v>
       </c>
       <c r="J31" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K31" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0304882420339303</v>
+        <v>0.02517278794085109</v>
       </c>
       <c r="M31" t="n">
-        <v>10.88984903654973</v>
+        <v>10.93162398681643</v>
       </c>
       <c r="N31" t="n">
-        <v>175.8042258894335</v>
+        <v>176.6658466985766</v>
       </c>
       <c r="O31" t="n">
-        <v>13.25911859398782</v>
+        <v>13.2915705128693</v>
       </c>
       <c r="P31" t="n">
-        <v>352.5052371475876</v>
+        <v>352.243754325329</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -28551,28 +28787,28 @@
         <v>0.0455</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3675467687378557</v>
+        <v>-0.3439350346365366</v>
       </c>
       <c r="J32" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K32" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08627037509019864</v>
+        <v>0.07653567652901727</v>
       </c>
       <c r="M32" t="n">
-        <v>7.85174644649192</v>
+        <v>7.897263865769813</v>
       </c>
       <c r="N32" t="n">
-        <v>91.46075966579505</v>
+        <v>92.32384373978894</v>
       </c>
       <c r="O32" t="n">
-        <v>9.563511889771197</v>
+        <v>9.608529738715957</v>
       </c>
       <c r="P32" t="n">
-        <v>351.7510333532841</v>
+        <v>351.5345115057788</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -28629,28 +28865,28 @@
         <v>0.0372</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8018620393619688</v>
+        <v>-0.7789578569772927</v>
       </c>
       <c r="J33" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K33" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L33" t="n">
-        <v>0.223000225156297</v>
+        <v>0.2147793397920945</v>
       </c>
       <c r="M33" t="n">
-        <v>9.462549574770351</v>
+        <v>9.460681846363766</v>
       </c>
       <c r="N33" t="n">
-        <v>146.5874767937689</v>
+        <v>146.8380123043224</v>
       </c>
       <c r="O33" t="n">
-        <v>12.10733153067879</v>
+        <v>12.11767355164853</v>
       </c>
       <c r="P33" t="n">
-        <v>348.9799423086013</v>
+        <v>348.7725352771175</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -28688,7 +28924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH217"/>
+  <dimension ref="A1:AH219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65751,6 +65987,350 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>-35.29144091237356,173.1596153651748</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>-35.290946412460436,173.1589349160078</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>-35.290403982193304,173.15832770002731</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-35.28983938495461,173.15775434995768</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-35.289252789805595,173.1572146075472</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-35.28861185335006,173.15675789494674</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-35.28800865690014,173.1562435076353</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-35.287436281333356,173.15568201848816</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-35.28689410749068,173.15507437354336</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-35.2863574416769,173.15445830575416</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-35.28579860951959,173.1538761029417</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-35.285221998705985,173.15332106060345</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-35.284646147443546,173.15276661027264</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-35.284075286530374,173.15221278779154</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>-35.28347676457324,173.15169781281648</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>-35.28284298748197,173.15122685349638</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>-35.282156590354724,173.15083368066823</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>-35.281645712056594,173.1501810179471</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>-35.281087951032795,173.14959765992384</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>-35.28053787466892,173.14900293513193</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>-35.27993976882198,173.1484792106747</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>-35.27931882292047,173.14798924675753</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>-35.2787185294441,173.14746874472635</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>-35.278125232341054,173.1469378935277</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>-35.2775374970997,173.14639881393458</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>-35.27698197249683,173.14581803510416</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>-35.27644061425593,173.14522073262947</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>-35.27592103819432,173.14458864421994</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>-35.27534664551171,173.1440257238203</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>-35.27472889006767,173.14351949110772</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>-35.274141698488876,173.1429732947425</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>-35.27352036988726,173.14247172424865</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>-35.29147471933329,173.15956370680874</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>-35.29097678791581,173.15888850093862</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>-35.29042580741084,173.15829435005503</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-35.289850185012895,173.1577378469448</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-35.289263702318074,173.1571979327015</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-35.28862962831235,173.15673073401183</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-35.288037006725666,173.1562001878665</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-35.28746502477622,173.15563809723423</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-35.286916157143786,173.1550406806413</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-35.28637358508958,173.15443363781696</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-35.28581171543336,173.153856076434</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-35.28521980502168,173.15332441266526</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-35.28463718821003,173.15278026092037</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>-35.28406157019601,173.15223334378246</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>-35.28346081309536,173.15172139531785</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>-35.2828482089911,173.15121913408498</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>-35.282166918590704,173.15081841160574</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>-35.28168427058439,173.1501240135689</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>-35.281098279165064,173.1495823909548</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>-35.28056237517464,173.14896671386288</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>-35.279968343070834,173.14843696685878</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>-35.279348659382286,173.14794513697726</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>-35.27875789046864,173.1474105540127</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>-35.2781709620944,173.14687028741517</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>-35.27758517748913,173.14632832405366</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>-35.27700438540867,173.14578628433947</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>-35.27644140569459,173.14521967817262</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>-35.27589858949262,173.14461799356104</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>-35.27531773906912,173.14406351597776</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>-35.27471246879981,173.1435409601694</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>-35.27415836570616,173.1429515041267</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>-35.273525905109274,173.1424644875493</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
